--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e83f89e59bab3417/Documentos/Deportes/Cestoball/FCCF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juradoh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="8_{AE601FAE-3EE8-4984-9A26-AC51F77E0CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6728C40-68D6-42A6-9732-FF284B5DD7F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94856A67-EF57-4404-87FA-5251B79AABF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="780" windowWidth="20730" windowHeight="11160" xr2:uid="{E639BD86-AEE3-43B7-8971-8B51DE0A5668}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E639BD86-AEE3-43B7-8971-8B51DE0A5668}"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte a FCCF" sheetId="1" r:id="rId1"/>
     <sheet name="Crudo" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Aux" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Para importar" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="Aux" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,18 +39,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="75">
   <si>
     <t>Club:</t>
+  </si>
+  <si>
+    <t>Vélez</t>
   </si>
   <si>
     <t>Torneo:</t>
   </si>
   <si>
+    <t>Apertura 2026</t>
+  </si>
+  <si>
+    <t>Fecha:</t>
+  </si>
+  <si>
+    <t>Rival:</t>
+  </si>
+  <si>
+    <t>Avellaneda</t>
+  </si>
+  <si>
     <t>Categoría:</t>
   </si>
   <si>
-    <t>Fecha:</t>
+    <t>Primera A</t>
   </si>
   <si>
     <t>1er tiempo</t>
@@ -73,10 +89,31 @@
     <t>Nombre</t>
   </si>
   <si>
+    <t>Lanza
+mientos</t>
+  </si>
+  <si>
     <t>Goles</t>
   </si>
   <si>
     <t>Rebotes</t>
+  </si>
+  <si>
+    <t>Recu
+peros</t>
+  </si>
+  <si>
+    <t>Pér
+didas</t>
+  </si>
+  <si>
+    <t>Faltas</t>
+  </si>
+  <si>
+    <t>Recuperos</t>
+  </si>
+  <si>
+    <t>Pérdidas</t>
   </si>
   <si>
     <t>Dobles</t>
@@ -97,64 +134,40 @@
     <t>Defensivos</t>
   </si>
   <si>
-    <t>Recuperos</t>
+    <t>LUCIA COSTA</t>
   </si>
   <si>
-    <t>Recu
-peros</t>
+    <t>MARIELA ELIAS</t>
   </si>
   <si>
-    <t>Pérdidas</t>
+    <t>MALENA ZUCCARINO</t>
   </si>
   <si>
-    <t>Pér
-didas</t>
+    <t>JIMENA GARCIA</t>
   </si>
   <si>
-    <t>Faltas</t>
+    <t>SOFIA NAÓN</t>
   </si>
   <si>
-    <t>Lanza
-mientos</t>
+    <t>VICTORIA FONTAN</t>
   </si>
   <si>
-    <t>Estadísticas | Reporte a FCCF v1</t>
+    <t>ZAHIRA HERRERA</t>
   </si>
   <si>
-    <t>Rival:</t>
+    <t>LUCILA GRANATELLI</t>
   </si>
   <si>
-    <t>APV</t>
+    <t>MARIA PAZ GOMEZ</t>
   </si>
   <si>
-    <t>Avellaneda</t>
+    <t>LUCIANA BRINGAS</t>
   </si>
   <si>
-    <t>Ballester</t>
+    <t>CANDELA THIM</t>
   </si>
   <si>
-    <t>CEF La Plata</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>GEVP</t>
-  </si>
-  <si>
-    <t>Hacoaj</t>
-  </si>
-  <si>
-    <t>San Martín</t>
-  </si>
-  <si>
-    <t>SITAS</t>
-  </si>
-  <si>
-    <t>Social Parque</t>
-  </si>
-  <si>
-    <t>Vélez</t>
+    <t>Estadísticas | Reporte a FCCF v2</t>
   </si>
   <si>
     <t>Categoría</t>
@@ -181,22 +194,22 @@
     <t>Nombre jugador</t>
   </si>
   <si>
-    <t>Apertura 2024</t>
+    <t>Masculino</t>
   </si>
   <si>
-    <t>Primera A</t>
+    <t>APV</t>
   </si>
   <si>
-    <t>Masculino</t>
+    <t>Apertura 2024</t>
   </si>
   <si>
     <t>APV masc A</t>
   </si>
   <si>
-    <t>APV masc B</t>
+    <t>Clausura 2024</t>
   </si>
   <si>
-    <t>Clausura 2024</t>
+    <t>APV masc B</t>
   </si>
   <si>
     <t>Apertura 2025</t>
@@ -205,25 +218,46 @@
     <t>Clausura 2025</t>
   </si>
   <si>
-    <t>Apertura 2026</t>
+    <t>Ballester</t>
+  </si>
+  <si>
+    <t>CEF La Plata</t>
   </si>
   <si>
     <t>Clausura 2026</t>
   </si>
   <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
     <t>Apertura 2027</t>
+  </si>
+  <si>
+    <t>GEVP</t>
   </si>
   <si>
     <t>Clausura 2027</t>
   </si>
   <si>
+    <t>Hacoaj</t>
+  </si>
+  <si>
     <t>Apertura 2028</t>
+  </si>
+  <si>
+    <t>San Martín</t>
   </si>
   <si>
     <t>Clausura 2028</t>
   </si>
   <si>
+    <t>SITAS</t>
+  </si>
+  <si>
     <t>Apertura 2029</t>
+  </si>
+  <si>
+    <t>Social Parque</t>
   </si>
   <si>
     <t>Clausura 2029</t>
@@ -239,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -651,106 +685,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -769,28 +718,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -823,29 +750,171 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1184,8 +1253,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AY24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:AQ24"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="6.7109375" customWidth="1"/>
@@ -1194,1556 +1263,1722 @@
     <col min="36" max="43" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-    </row>
-    <row r="2" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="42" t="s">
+    <row r="2" spans="2:43">
+      <c r="B2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="48"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
-      <c r="AX2" s="1"/>
-      <c r="AY2" s="1"/>
-    </row>
-    <row r="3" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="1"/>
-      <c r="AM3" s="1"/>
-      <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1"/>
-      <c r="AQ3" s="1"/>
-      <c r="AR3" s="1"/>
-      <c r="AS3" s="1"/>
-      <c r="AT3" s="1"/>
-      <c r="AU3" s="1"/>
-      <c r="AV3" s="1"/>
-      <c r="AW3" s="1"/>
-      <c r="AX3" s="1"/>
-      <c r="AY3" s="1"/>
-    </row>
-    <row r="4" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="40"/>
+    </row>
+    <row r="3" spans="2:43" ht="7.5" customHeight="1"/>
+    <row r="4" spans="2:43">
+      <c r="B4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
+      <c r="G4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="46"/>
+      <c r="I4" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="44"/>
+    </row>
+    <row r="5" spans="2:43" ht="15" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:43" ht="15" thickBot="1">
+      <c r="D6" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="60"/>
+    </row>
+    <row r="7" spans="2:43" ht="15" customHeight="1">
+      <c r="B7" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="67"/>
+      <c r="I7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="S7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="U7" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC7" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF7" s="53"/>
+      <c r="AG7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH7" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ7" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL7" s="65"/>
+      <c r="AM7" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN7" s="65"/>
+      <c r="AO7" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP7" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ7" s="54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:43">
+      <c r="B8" s="69"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="43" t="s">
+      <c r="H8" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="52"/>
+      <c r="AC8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE8" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF8" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="63"/>
+      <c r="AJ8" s="64"/>
+      <c r="AK8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM8" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="AN8" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO8" s="61"/>
+      <c r="AP8" s="61"/>
+      <c r="AQ8" s="54"/>
+    </row>
+    <row r="9" spans="2:43" ht="30" customHeight="1">
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>4</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16">
         <v>2</v>
       </c>
-      <c r="H4" s="44"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="1"/>
-    </row>
-    <row r="5" spans="2:51" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
-      <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1"/>
-      <c r="AQ5" s="1"/>
-    </row>
-    <row r="6" spans="2:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="10" t="s">
+      <c r="H9" s="16">
+        <v>1</v>
+      </c>
+      <c r="I9" s="16">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16">
+        <v>2</v>
+      </c>
+      <c r="K9" s="17">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0</v>
+      </c>
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="16">
+        <v>1</v>
+      </c>
+      <c r="P9" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0</v>
+      </c>
+      <c r="R9" s="16">
+        <v>1</v>
+      </c>
+      <c r="S9" s="17">
+        <v>5</v>
+      </c>
+      <c r="T9" s="14"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="8">
+        <f t="shared" ref="AJ9:AJ20" si="0">+D9+L9+T9+AB9</f>
         <v>4</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="15" t="s">
+      <c r="AK9" s="4">
+        <f t="shared" ref="AK9:AK20" si="1">+E9+M9+U9+AC9</f>
+        <v>1</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" ref="AL9:AL20" si="2">+F9+N9+V9+AD9</f>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="4">
+        <f t="shared" ref="AM9:AM20" si="3">+G9+O9+W9+AE9</f>
+        <v>3</v>
+      </c>
+      <c r="AN9" s="4">
+        <f t="shared" ref="AN9:AN20" si="4">+H9+P9+X9+AF9</f>
+        <v>1</v>
+      </c>
+      <c r="AO9" s="4">
+        <f t="shared" ref="AO9:AQ9" si="5">+I9+Q9+Y9+AG9</f>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="4">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:43" ht="30" customHeight="1">
+      <c r="B10" s="14">
         <v>5</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="10" t="s">
+      <c r="C10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14">
+        <v>1</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0</v>
+      </c>
+      <c r="N10" s="16">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16">
+        <v>0</v>
+      </c>
+      <c r="P10" s="16">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>2</v>
+      </c>
+      <c r="R10" s="16">
+        <v>4</v>
+      </c>
+      <c r="S10" s="17">
+        <v>5</v>
+      </c>
+      <c r="T10" s="14"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AO10" s="4">
+        <f t="shared" ref="AO10:AQ10" si="6">+I10+Q10+Y10+AG10</f>
+        <v>2</v>
+      </c>
+      <c r="AP10" s="4">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:43" ht="30" customHeight="1">
+      <c r="B11" s="14">
         <v>6</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="15" t="s">
+      <c r="C11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14">
+        <v>4</v>
+      </c>
+      <c r="M11" s="16">
+        <v>2</v>
+      </c>
+      <c r="N11" s="16">
+        <v>0</v>
+      </c>
+      <c r="O11" s="16">
+        <v>2</v>
+      </c>
+      <c r="P11" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0</v>
+      </c>
+      <c r="R11" s="16">
+        <v>0</v>
+      </c>
+      <c r="S11" s="17">
+        <v>3</v>
+      </c>
+      <c r="T11" s="14"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK11" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AL11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AN11" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AO11" s="4">
+        <f t="shared" ref="AO11:AQ11" si="7">+I11+Q11+Y11+AG11</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:43" ht="30" customHeight="1">
+      <c r="B12" s="14">
         <v>7</v>
       </c>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="20" t="s">
+      <c r="C12" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="14">
+        <v>11</v>
+      </c>
+      <c r="E12" s="16">
+        <v>5</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16">
+        <v>2</v>
+      </c>
+      <c r="K12" s="17">
+        <v>2</v>
+      </c>
+      <c r="L12" s="14">
+        <v>9</v>
+      </c>
+      <c r="M12" s="16">
+        <v>4</v>
+      </c>
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16">
+        <v>1</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>0</v>
+      </c>
+      <c r="R12" s="16">
+        <v>1</v>
+      </c>
+      <c r="S12" s="17">
+        <v>1</v>
+      </c>
+      <c r="T12" s="14"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK12" s="4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="AL12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AN12" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" ref="AO12:AQ12" si="8">+I12+Q12+Y12+AG12</f>
+        <v>1</v>
+      </c>
+      <c r="AP12" s="4">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:43" ht="30" customHeight="1">
+      <c r="B13" s="14">
         <v>8</v>
       </c>
-      <c r="AK6" s="21"/>
-      <c r="AL6" s="21"/>
-      <c r="AM6" s="21"/>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="21"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="22"/>
-    </row>
-    <row r="7" spans="2:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="31" t="s">
+      <c r="C13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="14">
+        <v>6</v>
+      </c>
+      <c r="E13" s="16">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <v>3</v>
+      </c>
+      <c r="I13" s="16">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
+        <v>3</v>
+      </c>
+      <c r="K13" s="17">
+        <v>2</v>
+      </c>
+      <c r="L13" s="14">
+        <v>8</v>
+      </c>
+      <c r="M13" s="16">
+        <v>5</v>
+      </c>
+      <c r="N13" s="16">
+        <v>0</v>
+      </c>
+      <c r="O13" s="16">
+        <v>2</v>
+      </c>
+      <c r="P13" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>1</v>
+      </c>
+      <c r="R13" s="16">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>3</v>
+      </c>
+      <c r="T13" s="14"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK13" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AL13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AN13" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AO13" s="4">
+        <f t="shared" ref="AO13:AQ13" si="9">+I13+Q13+Y13+AG13</f>
+        <v>1</v>
+      </c>
+      <c r="AP13" s="4">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:43" ht="30" customHeight="1">
+      <c r="B14" s="14">
         <v>9</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C14" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16">
+        <v>7</v>
+      </c>
+      <c r="I14" s="16">
+        <v>2</v>
+      </c>
+      <c r="J14" s="16">
+        <v>1</v>
+      </c>
+      <c r="K14" s="17">
+        <v>3</v>
+      </c>
+      <c r="L14" s="14">
+        <v>4</v>
+      </c>
+      <c r="M14" s="16">
+        <v>2</v>
+      </c>
+      <c r="N14" s="16">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16">
         <v>10</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="Q14" s="16">
+        <v>0</v>
+      </c>
+      <c r="R14" s="16">
+        <v>0</v>
+      </c>
+      <c r="S14" s="17">
+        <v>1</v>
+      </c>
+      <c r="T14" s="14"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK14" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AL14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="4">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AO14" s="4">
+        <f t="shared" ref="AO14:AQ14" si="10">+I14+Q14+Y14+AG14</f>
+        <v>2</v>
+      </c>
+      <c r="AP14" s="4">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="5">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:43" ht="30" customHeight="1">
+      <c r="B15" s="14">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>1</v>
+      </c>
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
+        <v>1</v>
+      </c>
+      <c r="K15" s="17">
+        <v>3</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="16">
+        <v>0</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>1</v>
+      </c>
+      <c r="R15" s="16">
+        <v>0</v>
+      </c>
+      <c r="S15" s="17">
+        <v>3</v>
+      </c>
+      <c r="T15" s="14"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AO15" s="4">
+        <f t="shared" ref="AO15:AQ15" si="11">+I15+Q15+Y15+AG15</f>
+        <v>1</v>
+      </c>
+      <c r="AP15" s="4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="5">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:43" ht="30" customHeight="1">
+      <c r="B16" s="14">
         <v>11</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
+      <c r="C16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="14">
+        <v>9</v>
+      </c>
+      <c r="E16" s="16">
+        <v>6</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>4</v>
+      </c>
+      <c r="L16" s="14">
+        <v>7</v>
+      </c>
+      <c r="M16" s="16">
+        <v>5</v>
+      </c>
+      <c r="N16" s="16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <v>2</v>
+      </c>
+      <c r="P16" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>0</v>
+      </c>
+      <c r="R16" s="16">
+        <v>1</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="14"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AK16" s="4">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="AL16" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AN16" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AO16" s="4">
+        <f t="shared" ref="AO16:AQ16" si="12">+I16+Q16+Y16+AG16</f>
+        <v>0</v>
+      </c>
+      <c r="AP16" s="4">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="5">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:43" ht="30" customHeight="1">
+      <c r="B17" s="14">
         <v>12</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="14" t="s">
+      <c r="C17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16">
+        <v>1</v>
+      </c>
+      <c r="J17" s="16">
+        <v>0</v>
+      </c>
+      <c r="K17" s="17">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>10</v>
+      </c>
+      <c r="M17" s="16">
+        <v>5</v>
+      </c>
+      <c r="N17" s="16">
+        <v>2</v>
+      </c>
+      <c r="O17" s="16">
+        <v>1</v>
+      </c>
+      <c r="P17" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
+        <v>1</v>
+      </c>
+      <c r="S17" s="17">
+        <v>1</v>
+      </c>
+      <c r="T17" s="14"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AK17" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AL17" s="4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AM17" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AN17" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AO17" s="4">
+        <f t="shared" ref="AO17:AQ17" si="13">+I17+Q17+Y17+AG17</f>
+        <v>1</v>
+      </c>
+      <c r="AP17" s="4">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:43" ht="30" customHeight="1">
+      <c r="B18" s="14">
+        <v>14</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>1</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0</v>
+      </c>
+      <c r="J18" s="16">
+        <v>0</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" s="14">
+        <v>1</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0</v>
+      </c>
+      <c r="N18" s="16">
+        <v>0</v>
+      </c>
+      <c r="O18" s="16">
+        <v>0</v>
+      </c>
+      <c r="P18" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>1</v>
+      </c>
+      <c r="R18" s="16">
+        <v>0</v>
+      </c>
+      <c r="S18" s="17">
+        <v>4</v>
+      </c>
+      <c r="T18" s="14"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK18" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="4">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AO18" s="4">
+        <f t="shared" ref="AO18:AQ18" si="14">+I18+Q18+Y18+AG18</f>
+        <v>1</v>
+      </c>
+      <c r="AP18" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="5">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:43" ht="30" customHeight="1">
+      <c r="B19" s="14">
+        <v>15</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>4</v>
+      </c>
+      <c r="E19" s="16">
+        <v>1</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="16">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
+        <v>0</v>
+      </c>
+      <c r="J19" s="16">
+        <v>1</v>
+      </c>
+      <c r="K19" s="17">
+        <v>2</v>
+      </c>
+      <c r="L19" s="14">
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0</v>
+      </c>
+      <c r="N19" s="16">
+        <v>0</v>
+      </c>
+      <c r="O19" s="16">
+        <v>0</v>
+      </c>
+      <c r="P19" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16">
+        <v>0</v>
+      </c>
+      <c r="S19" s="17">
+        <v>0</v>
+      </c>
+      <c r="T19" s="14"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK19" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AL19" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AN19" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="4">
+        <f t="shared" ref="AO19:AQ19" si="15">+I19+Q19+Y19+AG19</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="4">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="5">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:43" ht="30" customHeight="1">
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="20"/>
+      <c r="AH20" s="20"/>
+      <c r="AI20" s="21"/>
+      <c r="AJ20" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="10">
+        <f t="shared" ref="AO20:AQ20" si="16">+I20+Q20+Y20+AG20</f>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="10">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:43" ht="7.5" customHeight="1" thickBot="1"/>
+    <row r="22" spans="2:43" ht="30" customHeight="1" thickBot="1">
+      <c r="B22" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="22">
+        <f>SUM(D9:D20)</f>
+        <v>36</v>
+      </c>
+      <c r="E22" s="23">
+        <f t="shared" ref="E22:AQ22" si="17">SUM(E9:E20)</f>
+        <v>16</v>
+      </c>
+      <c r="F22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="23">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="H22" s="23">
+        <f t="shared" si="17"/>
+        <v>14</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="J22" s="23">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="K22" s="24">
+        <f t="shared" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="L22" s="25">
+        <f t="shared" si="17"/>
+        <v>44</v>
+      </c>
+      <c r="M22" s="26">
+        <f t="shared" si="17"/>
         <v>23</v>
       </c>
-      <c r="L7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD7" s="7"/>
-      <c r="AE7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF7" s="7"/>
-      <c r="AG7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AH7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK7" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL7" s="24"/>
-      <c r="AM7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN7" s="24"/>
-      <c r="AO7" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AP7" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ7" s="26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="4" t="s">
+      <c r="N22" s="26">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="O22" s="26">
+        <f t="shared" si="17"/>
+        <v>9</v>
+      </c>
+      <c r="P22" s="26">
+        <f t="shared" si="17"/>
+        <v>16</v>
+      </c>
+      <c r="Q22" s="26">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="R22" s="26">
+        <f t="shared" si="17"/>
+        <v>8</v>
+      </c>
+      <c r="S22" s="27">
+        <f t="shared" si="17"/>
+        <v>26</v>
+      </c>
+      <c r="T22" s="22">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="24">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="25">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="26">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="27">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="22">
+        <f t="shared" si="17"/>
+        <v>80</v>
+      </c>
+      <c r="AK22" s="23">
+        <f t="shared" si="17"/>
+        <v>39</v>
+      </c>
+      <c r="AL22" s="23">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="AM22" s="23">
+        <f t="shared" si="17"/>
         <v>13</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="18"/>
-      <c r="AC8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="23"/>
-      <c r="AK8" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL8" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM8" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="AN8" s="28" t="s">
+      <c r="AN22" s="23">
+        <f t="shared" si="17"/>
+        <v>30</v>
+      </c>
+      <c r="AO22" s="23">
+        <f t="shared" si="17"/>
+        <v>9</v>
+      </c>
+      <c r="AP22" s="23">
+        <f t="shared" si="17"/>
         <v>18</v>
       </c>
-      <c r="AO8" s="25"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="26"/>
-    </row>
-    <row r="9" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="49"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="52"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="37">
-        <f>+D9+L9+T9+AB9</f>
-        <v>0</v>
-      </c>
-      <c r="AK9" s="29">
-        <f>+E9+M9+U9+AC9</f>
-        <v>0</v>
-      </c>
-      <c r="AL9" s="29">
-        <f>+F9+N9+V9+AD9</f>
-        <v>0</v>
-      </c>
-      <c r="AM9" s="29">
-        <f>+G9+O9+W9+AE9</f>
-        <v>0</v>
-      </c>
-      <c r="AN9" s="29">
-        <f>+H9+P9+X9+AF9</f>
-        <v>0</v>
-      </c>
-      <c r="AO9" s="29">
-        <f t="shared" ref="AO9:AQ9" si="0">+I9+Q9+Y9+AG9</f>
-        <v>0</v>
-      </c>
-      <c r="AP9" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="49"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="52"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="51"/>
-      <c r="AE10" s="51"/>
-      <c r="AF10" s="51"/>
-      <c r="AG10" s="51"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="52"/>
-      <c r="AJ10" s="37">
-        <f>+D10+L10+T10+AB10</f>
-        <v>0</v>
-      </c>
-      <c r="AK10" s="29">
-        <f>+E10+M10+U10+AC10</f>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="29">
-        <f>+F10+N10+V10+AD10</f>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="29">
-        <f>+G10+O10+W10+AE10</f>
-        <v>0</v>
-      </c>
-      <c r="AN10" s="29">
-        <f>+H10+P10+X10+AF10</f>
-        <v>0</v>
-      </c>
-      <c r="AO10" s="29">
-        <f t="shared" ref="AO10:AQ10" si="1">+I10+Q10+Y10+AG10</f>
-        <v>0</v>
-      </c>
-      <c r="AP10" s="29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="51"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="51"/>
-      <c r="AE11" s="51"/>
-      <c r="AF11" s="51"/>
-      <c r="AG11" s="51"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="37">
-        <f>+D11+L11+T11+AB11</f>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="29">
-        <f>+E11+M11+U11+AC11</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="29">
-        <f>+F11+N11+V11+AD11</f>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="29">
-        <f>+G11+O11+W11+AE11</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="29">
-        <f>+H11+P11+X11+AF11</f>
-        <v>0</v>
-      </c>
-      <c r="AO11" s="29">
-        <f t="shared" ref="AO11:AQ11" si="2">+I11+Q11+Y11+AG11</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="29">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="52"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="51"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="51"/>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="52"/>
-      <c r="AJ12" s="37">
-        <f>+D12+L12+T12+AB12</f>
-        <v>0</v>
-      </c>
-      <c r="AK12" s="29">
-        <f>+E12+M12+U12+AC12</f>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="29">
-        <f>+F12+N12+V12+AD12</f>
-        <v>0</v>
-      </c>
-      <c r="AM12" s="29">
-        <f>+G12+O12+W12+AE12</f>
-        <v>0</v>
-      </c>
-      <c r="AN12" s="29">
-        <f>+H12+P12+X12+AF12</f>
-        <v>0</v>
-      </c>
-      <c r="AO12" s="29">
-        <f t="shared" ref="AO12:AQ12" si="3">+I12+Q12+Y12+AG12</f>
-        <v>0</v>
-      </c>
-      <c r="AP12" s="29">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-      <c r="AA13" s="52"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="51"/>
-      <c r="AD13" s="51"/>
-      <c r="AE13" s="51"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="52"/>
-      <c r="AJ13" s="37">
-        <f>+D13+L13+T13+AB13</f>
-        <v>0</v>
-      </c>
-      <c r="AK13" s="29">
-        <f>+E13+M13+U13+AC13</f>
-        <v>0</v>
-      </c>
-      <c r="AL13" s="29">
-        <f>+F13+N13+V13+AD13</f>
-        <v>0</v>
-      </c>
-      <c r="AM13" s="29">
-        <f>+G13+O13+W13+AE13</f>
-        <v>0</v>
-      </c>
-      <c r="AN13" s="29">
-        <f>+H13+P13+X13+AF13</f>
-        <v>0</v>
-      </c>
-      <c r="AO13" s="29">
-        <f t="shared" ref="AO13:AQ13" si="4">+I13+Q13+Y13+AG13</f>
-        <v>0</v>
-      </c>
-      <c r="AP13" s="29">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="30">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="49"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="51"/>
-      <c r="X14" s="51"/>
-      <c r="Y14" s="51"/>
-      <c r="Z14" s="51"/>
-      <c r="AA14" s="52"/>
-      <c r="AB14" s="49"/>
-      <c r="AC14" s="51"/>
-      <c r="AD14" s="51"/>
-      <c r="AE14" s="51"/>
-      <c r="AF14" s="51"/>
-      <c r="AG14" s="51"/>
-      <c r="AH14" s="51"/>
-      <c r="AI14" s="52"/>
-      <c r="AJ14" s="37">
-        <f>+D14+L14+T14+AB14</f>
-        <v>0</v>
-      </c>
-      <c r="AK14" s="29">
-        <f>+E14+M14+U14+AC14</f>
-        <v>0</v>
-      </c>
-      <c r="AL14" s="29">
-        <f>+F14+N14+V14+AD14</f>
-        <v>0</v>
-      </c>
-      <c r="AM14" s="29">
-        <f>+G14+O14+W14+AE14</f>
-        <v>0</v>
-      </c>
-      <c r="AN14" s="29">
-        <f>+H14+P14+X14+AF14</f>
-        <v>0</v>
-      </c>
-      <c r="AO14" s="29">
-        <f t="shared" ref="AO14:AQ14" si="5">+I14+Q14+Y14+AG14</f>
-        <v>0</v>
-      </c>
-      <c r="AP14" s="29">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="30">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="51"/>
-      <c r="V15" s="51"/>
-      <c r="W15" s="51"/>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="51"/>
-      <c r="Z15" s="51"/>
-      <c r="AA15" s="52"/>
-      <c r="AB15" s="49"/>
-      <c r="AC15" s="51"/>
-      <c r="AD15" s="51"/>
-      <c r="AE15" s="51"/>
-      <c r="AF15" s="51"/>
-      <c r="AG15" s="51"/>
-      <c r="AH15" s="51"/>
-      <c r="AI15" s="52"/>
-      <c r="AJ15" s="37">
-        <f>+D15+L15+T15+AB15</f>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="29">
-        <f>+E15+M15+U15+AC15</f>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="29">
-        <f>+F15+N15+V15+AD15</f>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="29">
-        <f>+G15+O15+W15+AE15</f>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="29">
-        <f>+H15+P15+X15+AF15</f>
-        <v>0</v>
-      </c>
-      <c r="AO15" s="29">
-        <f t="shared" ref="AO15:AQ15" si="6">+I15+Q15+Y15+AG15</f>
-        <v>0</v>
-      </c>
-      <c r="AP15" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="30">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:51" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="51"/>
-      <c r="AA16" s="52"/>
-      <c r="AB16" s="49"/>
-      <c r="AC16" s="51"/>
-      <c r="AD16" s="51"/>
-      <c r="AE16" s="51"/>
-      <c r="AF16" s="51"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="51"/>
-      <c r="AI16" s="52"/>
-      <c r="AJ16" s="37">
-        <f>+D16+L16+T16+AB16</f>
-        <v>0</v>
-      </c>
-      <c r="AK16" s="29">
-        <f>+E16+M16+U16+AC16</f>
-        <v>0</v>
-      </c>
-      <c r="AL16" s="29">
-        <f>+F16+N16+V16+AD16</f>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="29">
-        <f>+G16+O16+W16+AE16</f>
-        <v>0</v>
-      </c>
-      <c r="AN16" s="29">
-        <f>+H16+P16+X16+AF16</f>
-        <v>0</v>
-      </c>
-      <c r="AO16" s="29">
-        <f t="shared" ref="AO16:AQ16" si="7">+I16+Q16+Y16+AG16</f>
-        <v>0</v>
-      </c>
-      <c r="AP16" s="29">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="30">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="51"/>
-      <c r="V17" s="51"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
-      <c r="Y17" s="51"/>
-      <c r="Z17" s="51"/>
-      <c r="AA17" s="52"/>
-      <c r="AB17" s="49"/>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
-      <c r="AE17" s="51"/>
-      <c r="AF17" s="51"/>
-      <c r="AG17" s="51"/>
-      <c r="AH17" s="51"/>
-      <c r="AI17" s="52"/>
-      <c r="AJ17" s="37">
-        <f>+D17+L17+T17+AB17</f>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="29">
-        <f>+E17+M17+U17+AC17</f>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="29">
-        <f>+F17+N17+V17+AD17</f>
-        <v>0</v>
-      </c>
-      <c r="AM17" s="29">
-        <f>+G17+O17+W17+AE17</f>
-        <v>0</v>
-      </c>
-      <c r="AN17" s="29">
-        <f>+H17+P17+X17+AF17</f>
-        <v>0</v>
-      </c>
-      <c r="AO17" s="29">
-        <f t="shared" ref="AO17:AQ17" si="8">+I17+Q17+Y17+AG17</f>
-        <v>0</v>
-      </c>
-      <c r="AP17" s="29">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="30">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="51"/>
-      <c r="Z18" s="51"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="51"/>
-      <c r="AD18" s="51"/>
-      <c r="AE18" s="51"/>
-      <c r="AF18" s="51"/>
-      <c r="AG18" s="51"/>
-      <c r="AH18" s="51"/>
-      <c r="AI18" s="52"/>
-      <c r="AJ18" s="37">
-        <f>+D18+L18+T18+AB18</f>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="29">
-        <f>+E18+M18+U18+AC18</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="29">
-        <f>+F18+N18+V18+AD18</f>
-        <v>0</v>
-      </c>
-      <c r="AM18" s="29">
-        <f>+G18+O18+W18+AE18</f>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="29">
-        <f>+H18+P18+X18+AF18</f>
-        <v>0</v>
-      </c>
-      <c r="AO18" s="29">
-        <f t="shared" ref="AO18:AQ18" si="9">+I18+Q18+Y18+AG18</f>
-        <v>0</v>
-      </c>
-      <c r="AP18" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="30">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:43" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="51"/>
-      <c r="V19" s="51"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="51"/>
-      <c r="Y19" s="51"/>
-      <c r="Z19" s="51"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="49"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="51"/>
-      <c r="AE19" s="51"/>
-      <c r="AF19" s="51"/>
-      <c r="AG19" s="51"/>
-      <c r="AH19" s="51"/>
-      <c r="AI19" s="52"/>
-      <c r="AJ19" s="37">
-        <f>+D19+L19+T19+AB19</f>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="29">
-        <f>+E19+M19+U19+AC19</f>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="29">
-        <f>+F19+N19+V19+AD19</f>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="29">
-        <f>+G19+O19+W19+AE19</f>
-        <v>0</v>
-      </c>
-      <c r="AN19" s="29">
-        <f>+H19+P19+X19+AF19</f>
-        <v>0</v>
-      </c>
-      <c r="AO19" s="29">
-        <f t="shared" ref="AO19:AQ19" si="10">+I19+Q19+Y19+AG19</f>
-        <v>0</v>
-      </c>
-      <c r="AP19" s="29">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="30">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:43" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="56"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="55"/>
-      <c r="V20" s="55"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="55"/>
-      <c r="Y20" s="55"/>
-      <c r="Z20" s="55"/>
-      <c r="AA20" s="56"/>
-      <c r="AB20" s="53"/>
-      <c r="AC20" s="55"/>
-      <c r="AD20" s="55"/>
-      <c r="AE20" s="55"/>
-      <c r="AF20" s="55"/>
-      <c r="AG20" s="55"/>
-      <c r="AH20" s="55"/>
-      <c r="AI20" s="56"/>
-      <c r="AJ20" s="38">
-        <f>+D20+L20+T20+AB20</f>
-        <v>0</v>
-      </c>
-      <c r="AK20" s="39">
-        <f>+E20+M20+U20+AC20</f>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="39">
-        <f>+F20+N20+V20+AD20</f>
-        <v>0</v>
-      </c>
-      <c r="AM20" s="39">
-        <f>+G20+O20+W20+AE20</f>
-        <v>0</v>
-      </c>
-      <c r="AN20" s="39">
-        <f>+H20+P20+X20+AF20</f>
-        <v>0</v>
-      </c>
-      <c r="AO20" s="39">
-        <f t="shared" ref="AO20:AQ20" si="11">+I20+Q20+Y20+AG20</f>
-        <v>0</v>
-      </c>
-      <c r="AP20" s="39">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:43" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="1"/>
-      <c r="AI21" s="1"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="1"/>
-      <c r="AO21" s="1"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="1"/>
-    </row>
-    <row r="22" spans="2:43" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="57">
-        <f>SUM(D9:D20)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="58">
-        <f t="shared" ref="E22:AQ22" si="12">SUM(E9:E20)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="59">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="62">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="64">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="57">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="59">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="62">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AH22" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="64">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="57">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AK22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AO22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AP22" s="58">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="59">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1"/>
-      <c r="AI23" s="1"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="1"/>
-      <c r="AO23" s="1"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="1"/>
-    </row>
-    <row r="24" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B24" s="35" t="s">
-        <v>25</v>
+      <c r="AQ22" s="24">
+        <f t="shared" si="17"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:43" ht="7.5" customHeight="1"/>
+    <row r="24" spans="2:43">
+      <c r="B24" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lp4dnEDLhZYSizehWQjTecqFwGSJfnI0o72RDYBn3OJ1Bh2vZYIFu7iEiFbTENrpVB3JjHP8Iuk3ojZtvmd8Wg==" saltValue="hKeNEc5PZbAW85tVxxkftg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p7fIers6SmxwsqcoKSTKbxIZVsjjPqhJdelkBqeNyURgPQc6ig8kxuK3t6qGnZJ95xkPVj+bbX5d0IIUwpg/oQ==" saltValue="d53BfToyjZydW7HXtZ3KGA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="45">
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AM7:AN7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="T6:AA6"/>
+    <mergeCell ref="AB6:AI6"/>
+    <mergeCell ref="AJ6:AQ6"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AD7"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="C2:E2"/>
@@ -2752,43 +2987,13 @@
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:N4"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="L6:S6"/>
-    <mergeCell ref="T6:AA6"/>
-    <mergeCell ref="AB6:AI6"/>
-    <mergeCell ref="AJ6:AQ6"/>
-    <mergeCell ref="AO7:AO8"/>
-    <mergeCell ref="AP7:AP8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="D6:K6"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="K7:K8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AK7:AL7"/>
-    <mergeCell ref="AM7:AN7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AH8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="O7:P7"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9:B20" xr:uid="{A42240DA-97DC-4F2B-B6B5-97DEE74B9762}">
@@ -2806,6 +3011,9 @@
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;7&amp;K000000 ***Este documento está clasificado como USO INTERNO por MOVISTAR. ***This document is classified as INTERNAL USE by MOVISTAR.</oddFooter>
+  </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -2842,103 +3050,103 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA78724F-71A9-482D-BEEE-EC04E8E7B68D}">
   <dimension ref="A1:P49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="41"/>
+    <col min="3" max="3" width="11.42578125" style="12"/>
     <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
       <c r="P1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B2">
+        <v>Primera A</v>
+      </c>
+      <c r="B2" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C2" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E2">
+        <v>Vélez</v>
+      </c>
+      <c r="E2" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <f>+'Reporte a FCCF'!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="str">
         <f>+'Reporte a FCCF'!$C$9</f>
-        <v>0</v>
+        <v>LUCIA COSTA</v>
       </c>
       <c r="I2">
         <f>+'Reporte a FCCF'!D9</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <f>+'Reporte a FCCF'!E9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>+'Reporte a FCCF'!F9</f>
@@ -2946,11 +3154,11 @@
       </c>
       <c r="L2">
         <f>+'Reporte a FCCF'!G9</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <f>+'Reporte a FCCF'!H9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <f>+'Reporte a FCCF'!I9</f>
@@ -2958,44 +3166,44 @@
       </c>
       <c r="O2">
         <f>+'Reporte a FCCF'!J9</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2">
         <f>+'Reporte a FCCF'!K9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B3">
+        <v>Primera A</v>
+      </c>
+      <c r="B3" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C3" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
+        <v>Vélez</v>
+      </c>
+      <c r="E3" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <f>+'Reporte a FCCF'!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="H3" t="str">
         <f>+'Reporte a FCCF'!$C$10</f>
-        <v>0</v>
+        <v>MARIELA ELIAS</v>
       </c>
       <c r="I3">
         <f>+'Reporte a FCCF'!D10</f>
@@ -3030,37 +3238,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:16">
+      <c r="A4" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B4">
+        <v>Primera A</v>
+      </c>
+      <c r="B4" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C4" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E4">
+        <v>Vélez</v>
+      </c>
+      <c r="E4" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <f>+'Reporte a FCCF'!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="H4" t="str">
         <f>+'Reporte a FCCF'!$C$11</f>
-        <v>0</v>
+        <v>MALENA ZUCCARINO</v>
       </c>
       <c r="I4">
         <f>+'Reporte a FCCF'!D11</f>
@@ -3095,45 +3303,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:16">
+      <c r="A5" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B5">
+        <v>Primera A</v>
+      </c>
+      <c r="B5" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C5" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>Vélez</v>
+      </c>
+      <c r="E5" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <f>+'Reporte a FCCF'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="str">
         <f>+'Reporte a FCCF'!$C$12</f>
-        <v>0</v>
+        <v>JIMENA GARCIA</v>
       </c>
       <c r="I5">
         <f>+'Reporte a FCCF'!D12</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <f>+'Reporte a FCCF'!E12</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <f>+'Reporte a FCCF'!F12</f>
@@ -3149,56 +3357,56 @@
       </c>
       <c r="N5">
         <f>+'Reporte a FCCF'!I12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f>+'Reporte a FCCF'!J12</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5">
         <f>+'Reporte a FCCF'!K12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B6">
+        <v>Primera A</v>
+      </c>
+      <c r="B6" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C6" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v>Vélez</v>
+      </c>
+      <c r="E6" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <f>+'Reporte a FCCF'!$B$13</f>
-        <v>0</v>
-      </c>
-      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="H6" t="str">
         <f>+'Reporte a FCCF'!$C$13</f>
-        <v>0</v>
+        <v>SOFIA NAÓN</v>
       </c>
       <c r="I6">
         <f>+'Reporte a FCCF'!D13</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <f>+'Reporte a FCCF'!E13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f>+'Reporte a FCCF'!F13</f>
@@ -3210,7 +3418,7 @@
       </c>
       <c r="M6">
         <f>+'Reporte a FCCF'!H13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6">
         <f>+'Reporte a FCCF'!I13</f>
@@ -3218,48 +3426,48 @@
       </c>
       <c r="O6">
         <f>+'Reporte a FCCF'!J13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6">
         <f>+'Reporte a FCCF'!K13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B7">
+        <v>Primera A</v>
+      </c>
+      <c r="B7" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C7" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v>Vélez</v>
+      </c>
+      <c r="E7" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <f>+'Reporte a FCCF'!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="H7" t="str">
         <f>+'Reporte a FCCF'!$C$14</f>
-        <v>0</v>
+        <v>VICTORIA FONTAN</v>
       </c>
       <c r="I7">
         <f>+'Reporte a FCCF'!D14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f>+'Reporte a FCCF'!E14</f>
@@ -3275,52 +3483,52 @@
       </c>
       <c r="M7">
         <f>+'Reporte a FCCF'!H14</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <f>+'Reporte a FCCF'!I14</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7">
         <f>+'Reporte a FCCF'!J14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f>+'Reporte a FCCF'!K14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B8">
+        <v>Primera A</v>
+      </c>
+      <c r="B8" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C8" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E8">
+        <v>Vélez</v>
+      </c>
+      <c r="E8" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <f>+'Reporte a FCCF'!$B$15</f>
-        <v>0</v>
-      </c>
-      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="H8" t="str">
         <f>+'Reporte a FCCF'!$C$15</f>
-        <v>0</v>
+        <v>ZAHIRA HERRERA</v>
       </c>
       <c r="I8">
         <f>+'Reporte a FCCF'!D15</f>
@@ -3340,7 +3548,7 @@
       </c>
       <c r="M8">
         <f>+'Reporte a FCCF'!H15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <f>+'Reporte a FCCF'!I15</f>
@@ -3348,52 +3556,52 @@
       </c>
       <c r="O8">
         <f>+'Reporte a FCCF'!J15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <f>+'Reporte a FCCF'!K15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B9">
+        <v>Primera A</v>
+      </c>
+      <c r="B9" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C9" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E9">
+        <v>Vélez</v>
+      </c>
+      <c r="E9" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <f>+'Reporte a FCCF'!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="H9" t="str">
         <f>+'Reporte a FCCF'!$C$16</f>
-        <v>0</v>
+        <v>LUCILA GRANATELLI</v>
       </c>
       <c r="I9">
         <f>+'Reporte a FCCF'!D16</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <f>+'Reporte a FCCF'!E16</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <f>+'Reporte a FCCF'!F16</f>
@@ -3401,11 +3609,11 @@
       </c>
       <c r="L9">
         <f>+'Reporte a FCCF'!G16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
         <f>+'Reporte a FCCF'!H16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
         <f>+'Reporte a FCCF'!I16</f>
@@ -3417,44 +3625,44 @@
       </c>
       <c r="P9">
         <f>+'Reporte a FCCF'!K16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B10">
+        <v>Primera A</v>
+      </c>
+      <c r="B10" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C10" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E10">
+        <v>Vélez</v>
+      </c>
+      <c r="E10" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <f>+'Reporte a FCCF'!$B$17</f>
-        <v>0</v>
-      </c>
-      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="H10" t="str">
         <f>+'Reporte a FCCF'!$C$17</f>
-        <v>0</v>
+        <v>MARIA PAZ GOMEZ</v>
       </c>
       <c r="I10">
         <f>+'Reporte a FCCF'!D17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <f>+'Reporte a FCCF'!E17</f>
@@ -3474,7 +3682,7 @@
       </c>
       <c r="N10">
         <f>+'Reporte a FCCF'!I17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <f>+'Reporte a FCCF'!J17</f>
@@ -3485,37 +3693,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:16">
+      <c r="A11" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B11">
+        <v>Primera A</v>
+      </c>
+      <c r="B11" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C11" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E11">
+        <v>Vélez</v>
+      </c>
+      <c r="E11" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <f>+'Reporte a FCCF'!$B$18</f>
-        <v>0</v>
-      </c>
-      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="H11" t="str">
         <f>+'Reporte a FCCF'!$C$18</f>
-        <v>0</v>
+        <v>LUCIANA BRINGAS</v>
       </c>
       <c r="I11">
         <f>+'Reporte a FCCF'!D18</f>
@@ -3535,7 +3743,7 @@
       </c>
       <c r="M11">
         <f>+'Reporte a FCCF'!H18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <f>+'Reporte a FCCF'!I18</f>
@@ -3547,48 +3755,48 @@
       </c>
       <c r="P11">
         <f>+'Reporte a FCCF'!K18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B12">
+        <v>Primera A</v>
+      </c>
+      <c r="B12" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C12" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E12">
+        <v>Vélez</v>
+      </c>
+      <c r="E12" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <f>+'Reporte a FCCF'!$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="H12" t="str">
         <f>+'Reporte a FCCF'!$C$19</f>
-        <v>0</v>
+        <v>CANDELA THIM</v>
       </c>
       <c r="I12">
         <f>+'Reporte a FCCF'!D19</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <f>+'Reporte a FCCF'!E19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>+'Reporte a FCCF'!F19</f>
@@ -3596,7 +3804,7 @@
       </c>
       <c r="L12">
         <f>+'Reporte a FCCF'!G19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
         <f>+'Reporte a FCCF'!H19</f>
@@ -3608,36 +3816,36 @@
       </c>
       <c r="O12">
         <f>+'Reporte a FCCF'!J19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <f>+'Reporte a FCCF'!K19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B13">
+        <v>Primera A</v>
+      </c>
+      <c r="B13" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C13" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E13">
+        <v>Vélez</v>
+      </c>
+      <c r="E13" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <f>+'Reporte a FCCF'!$B$20</f>
@@ -3680,37 +3888,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:16">
+      <c r="A14" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B14">
+        <v>Primera A</v>
+      </c>
+      <c r="B14" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C14" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
+        <v>Vélez</v>
+      </c>
+      <c r="E14" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <f>+'Reporte a FCCF'!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
         <f>+'Reporte a FCCF'!$C$9</f>
-        <v>0</v>
+        <v>LUCIA COSTA</v>
       </c>
       <c r="I14">
         <f>+'Reporte a FCCF'!L9</f>
@@ -3726,7 +3934,7 @@
       </c>
       <c r="L14">
         <f>+'Reporte a FCCF'!O9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <f>+'Reporte a FCCF'!P9</f>
@@ -3738,48 +3946,48 @@
       </c>
       <c r="O14">
         <f>+'Reporte a FCCF'!R9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14">
         <f>+'Reporte a FCCF'!S9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B15">
+        <v>Primera A</v>
+      </c>
+      <c r="B15" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C15" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E15">
+        <v>Vélez</v>
+      </c>
+      <c r="E15" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <f>+'Reporte a FCCF'!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
         <f>+'Reporte a FCCF'!$C$10</f>
-        <v>0</v>
+        <v>MARIELA ELIAS</v>
       </c>
       <c r="I15">
         <f>+'Reporte a FCCF'!L10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <f>+'Reporte a FCCF'!M10</f>
@@ -3795,60 +4003,60 @@
       </c>
       <c r="M15">
         <f>+'Reporte a FCCF'!P10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <f>+'Reporte a FCCF'!Q10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <f>+'Reporte a FCCF'!R10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15">
         <f>+'Reporte a FCCF'!S10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B16">
+        <v>Primera A</v>
+      </c>
+      <c r="B16" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C16" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
+        <v>Vélez</v>
+      </c>
+      <c r="E16" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <f>+'Reporte a FCCF'!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="H16" t="str">
         <f>+'Reporte a FCCF'!$C$11</f>
-        <v>0</v>
+        <v>MALENA ZUCCARINO</v>
       </c>
       <c r="I16">
         <f>+'Reporte a FCCF'!L11</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16">
         <f>+'Reporte a FCCF'!M11</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <f>+'Reporte a FCCF'!N11</f>
@@ -3856,11 +4064,11 @@
       </c>
       <c r="L16">
         <f>+'Reporte a FCCF'!O11</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16">
         <f>+'Reporte a FCCF'!P11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16">
         <f>+'Reporte a FCCF'!Q11</f>
@@ -3872,48 +4080,48 @@
       </c>
       <c r="P16">
         <f>+'Reporte a FCCF'!S11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B17">
+        <v>Primera A</v>
+      </c>
+      <c r="B17" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C17" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
+        <v>Vélez</v>
+      </c>
+      <c r="E17" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <f>+'Reporte a FCCF'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="H17">
+        <v>7</v>
+      </c>
+      <c r="H17" t="str">
         <f>+'Reporte a FCCF'!$C$12</f>
-        <v>0</v>
+        <v>JIMENA GARCIA</v>
       </c>
       <c r="I17">
         <f>+'Reporte a FCCF'!L12</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <f>+'Reporte a FCCF'!M12</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <f>+'Reporte a FCCF'!N12</f>
@@ -3921,7 +4129,7 @@
       </c>
       <c r="L17">
         <f>+'Reporte a FCCF'!O12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17">
         <f>+'Reporte a FCCF'!P12</f>
@@ -3933,52 +4141,52 @@
       </c>
       <c r="O17">
         <f>+'Reporte a FCCF'!R12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17">
         <f>+'Reporte a FCCF'!S12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B18">
+        <v>Primera A</v>
+      </c>
+      <c r="B18" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C18" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
+        <v>Vélez</v>
+      </c>
+      <c r="E18" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <f>+'Reporte a FCCF'!$B$13</f>
-        <v>0</v>
-      </c>
-      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="H18" t="str">
         <f>+'Reporte a FCCF'!$C$13</f>
-        <v>0</v>
+        <v>SOFIA NAÓN</v>
       </c>
       <c r="I18">
         <f>+'Reporte a FCCF'!L13</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <f>+'Reporte a FCCF'!M13</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <f>+'Reporte a FCCF'!N13</f>
@@ -3986,7 +4194,7 @@
       </c>
       <c r="L18">
         <f>+'Reporte a FCCF'!O13</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18">
         <f>+'Reporte a FCCF'!P13</f>
@@ -3994,7 +4202,7 @@
       </c>
       <c r="N18">
         <f>+'Reporte a FCCF'!Q13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18">
         <f>+'Reporte a FCCF'!R13</f>
@@ -4002,48 +4210,48 @@
       </c>
       <c r="P18">
         <f>+'Reporte a FCCF'!S13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B19">
+        <v>Primera A</v>
+      </c>
+      <c r="B19" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C19" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
+        <v>Vélez</v>
+      </c>
+      <c r="E19" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <f>+'Reporte a FCCF'!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="H19" t="str">
         <f>+'Reporte a FCCF'!$C$14</f>
-        <v>0</v>
+        <v>VICTORIA FONTAN</v>
       </c>
       <c r="I19">
         <f>+'Reporte a FCCF'!L14</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19">
         <f>+'Reporte a FCCF'!M14</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <f>+'Reporte a FCCF'!N14</f>
@@ -4055,7 +4263,7 @@
       </c>
       <c r="M19">
         <f>+'Reporte a FCCF'!P14</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <f>+'Reporte a FCCF'!Q14</f>
@@ -4067,40 +4275,40 @@
       </c>
       <c r="P19">
         <f>+'Reporte a FCCF'!S14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B20">
+        <v>Primera A</v>
+      </c>
+      <c r="B20" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C20" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
+        <v>Vélez</v>
+      </c>
+      <c r="E20" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F20" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <f>+'Reporte a FCCF'!$B$15</f>
-        <v>0</v>
-      </c>
-      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="H20" t="str">
         <f>+'Reporte a FCCF'!$C$15</f>
-        <v>0</v>
+        <v>ZAHIRA HERRERA</v>
       </c>
       <c r="I20">
         <f>+'Reporte a FCCF'!L15</f>
@@ -4124,7 +4332,7 @@
       </c>
       <c r="N20">
         <f>+'Reporte a FCCF'!Q15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <f>+'Reporte a FCCF'!R15</f>
@@ -4132,48 +4340,48 @@
       </c>
       <c r="P20">
         <f>+'Reporte a FCCF'!S15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B21">
+        <v>Primera A</v>
+      </c>
+      <c r="B21" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C21" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
+        <v>Vélez</v>
+      </c>
+      <c r="E21" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <f>+'Reporte a FCCF'!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
+        <v>11</v>
+      </c>
+      <c r="H21" t="str">
         <f>+'Reporte a FCCF'!$C$16</f>
-        <v>0</v>
+        <v>LUCILA GRANATELLI</v>
       </c>
       <c r="I21">
         <f>+'Reporte a FCCF'!L16</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <f>+'Reporte a FCCF'!M16</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <f>+'Reporte a FCCF'!N16</f>
@@ -4181,7 +4389,7 @@
       </c>
       <c r="L21">
         <f>+'Reporte a FCCF'!O16</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21">
         <f>+'Reporte a FCCF'!P16</f>
@@ -4193,64 +4401,64 @@
       </c>
       <c r="O21">
         <f>+'Reporte a FCCF'!R16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <f>+'Reporte a FCCF'!S16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22" spans="1:16">
+      <c r="A22" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B22">
+        <v>Primera A</v>
+      </c>
+      <c r="B22" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C22" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
+        <v>Vélez</v>
+      </c>
+      <c r="E22" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <f>+'Reporte a FCCF'!$B$17</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
+        <v>12</v>
+      </c>
+      <c r="H22" t="str">
         <f>+'Reporte a FCCF'!$C$17</f>
-        <v>0</v>
+        <v>MARIA PAZ GOMEZ</v>
       </c>
       <c r="I22">
         <f>+'Reporte a FCCF'!L17</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <f>+'Reporte a FCCF'!M17</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <f>+'Reporte a FCCF'!N17</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22">
         <f>+'Reporte a FCCF'!O17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <f>+'Reporte a FCCF'!P17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
         <f>+'Reporte a FCCF'!Q17</f>
@@ -4258,48 +4466,48 @@
       </c>
       <c r="O22">
         <f>+'Reporte a FCCF'!R17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
         <f>+'Reporte a FCCF'!S17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B23">
+        <v>Primera A</v>
+      </c>
+      <c r="B23" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C23" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
+        <v>Vélez</v>
+      </c>
+      <c r="E23" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F23" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <f>+'Reporte a FCCF'!$B$18</f>
-        <v>0</v>
-      </c>
-      <c r="H23">
+        <v>14</v>
+      </c>
+      <c r="H23" t="str">
         <f>+'Reporte a FCCF'!$C$18</f>
-        <v>0</v>
+        <v>LUCIANA BRINGAS</v>
       </c>
       <c r="I23">
         <f>+'Reporte a FCCF'!L18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <f>+'Reporte a FCCF'!M18</f>
@@ -4315,11 +4523,11 @@
       </c>
       <c r="M23">
         <f>+'Reporte a FCCF'!P18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23">
         <f>+'Reporte a FCCF'!Q18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <f>+'Reporte a FCCF'!R18</f>
@@ -4327,40 +4535,40 @@
       </c>
       <c r="P23">
         <f>+'Reporte a FCCF'!S18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B24">
+        <v>Primera A</v>
+      </c>
+      <c r="B24" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C24" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
+        <v>Vélez</v>
+      </c>
+      <c r="E24" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <f>+'Reporte a FCCF'!$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="H24">
+        <v>15</v>
+      </c>
+      <c r="H24" t="str">
         <f>+'Reporte a FCCF'!$C$19</f>
-        <v>0</v>
+        <v>CANDELA THIM</v>
       </c>
       <c r="I24">
         <f>+'Reporte a FCCF'!L19</f>
@@ -4395,29 +4603,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="25" spans="1:16">
+      <c r="A25" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B25">
+        <v>Primera A</v>
+      </c>
+      <c r="B25" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C25" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
+        <v>Vélez</v>
+      </c>
+      <c r="E25" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F25" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <f>+'Reporte a FCCF'!$B$20</f>
@@ -4460,37 +4668,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="1:16">
+      <c r="A26" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B26">
+        <v>Primera A</v>
+      </c>
+      <c r="B26" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C26" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
+        <v>Vélez</v>
+      </c>
+      <c r="E26" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F26" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <f>+'Reporte a FCCF'!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="str">
         <f>+'Reporte a FCCF'!$C$9</f>
-        <v>0</v>
+        <v>LUCIA COSTA</v>
       </c>
       <c r="I26">
         <f>+'Reporte a FCCF'!T9</f>
@@ -4525,37 +4733,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="27" spans="1:16">
+      <c r="A27" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B27">
+        <v>Primera A</v>
+      </c>
+      <c r="B27" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C27" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
+        <v>Vélez</v>
+      </c>
+      <c r="E27" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <f>+'Reporte a FCCF'!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="str">
         <f>+'Reporte a FCCF'!$C$10</f>
-        <v>0</v>
+        <v>MARIELA ELIAS</v>
       </c>
       <c r="I27">
         <f>+'Reporte a FCCF'!T10</f>
@@ -4590,37 +4798,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="28" spans="1:16">
+      <c r="A28" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B28">
+        <v>Primera A</v>
+      </c>
+      <c r="B28" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C28" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E28">
+        <v>Vélez</v>
+      </c>
+      <c r="E28" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F28" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <f>+'Reporte a FCCF'!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="H28" t="str">
         <f>+'Reporte a FCCF'!$C$11</f>
-        <v>0</v>
+        <v>MALENA ZUCCARINO</v>
       </c>
       <c r="I28">
         <f>+'Reporte a FCCF'!T11</f>
@@ -4655,37 +4863,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="29" spans="1:16">
+      <c r="A29" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B29">
+        <v>Primera A</v>
+      </c>
+      <c r="B29" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C29" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
+        <v>Vélez</v>
+      </c>
+      <c r="E29" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F29" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <f>+'Reporte a FCCF'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="H29" t="str">
         <f>+'Reporte a FCCF'!$C$12</f>
-        <v>0</v>
+        <v>JIMENA GARCIA</v>
       </c>
       <c r="I29">
         <f>+'Reporte a FCCF'!T12</f>
@@ -4720,37 +4928,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30" spans="1:16">
+      <c r="A30" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B30">
+        <v>Primera A</v>
+      </c>
+      <c r="B30" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C30" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E30">
+        <v>Vélez</v>
+      </c>
+      <c r="E30" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F30" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G30">
         <f>+'Reporte a FCCF'!$B$13</f>
-        <v>0</v>
-      </c>
-      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="H30" t="str">
         <f>+'Reporte a FCCF'!$C$13</f>
-        <v>0</v>
+        <v>SOFIA NAÓN</v>
       </c>
       <c r="I30">
         <f>+'Reporte a FCCF'!T13</f>
@@ -4785,37 +4993,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="31" spans="1:16">
+      <c r="A31" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B31">
+        <v>Primera A</v>
+      </c>
+      <c r="B31" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C31" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E31">
+        <v>Vélez</v>
+      </c>
+      <c r="E31" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F31" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G31">
         <f>+'Reporte a FCCF'!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H31">
+        <v>9</v>
+      </c>
+      <c r="H31" t="str">
         <f>+'Reporte a FCCF'!$C$14</f>
-        <v>0</v>
+        <v>VICTORIA FONTAN</v>
       </c>
       <c r="I31">
         <f>+'Reporte a FCCF'!T14</f>
@@ -4850,37 +5058,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="32" spans="1:16">
+      <c r="A32" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B32">
+        <v>Primera A</v>
+      </c>
+      <c r="B32" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C32" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E32">
+        <v>Vélez</v>
+      </c>
+      <c r="E32" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F32" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <f>+'Reporte a FCCF'!$B$15</f>
-        <v>0</v>
-      </c>
-      <c r="H32">
+        <v>10</v>
+      </c>
+      <c r="H32" t="str">
         <f>+'Reporte a FCCF'!$C$15</f>
-        <v>0</v>
+        <v>ZAHIRA HERRERA</v>
       </c>
       <c r="I32">
         <f>+'Reporte a FCCF'!T15</f>
@@ -4915,37 +5123,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="33" spans="1:16">
+      <c r="A33" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B33">
+        <v>Primera A</v>
+      </c>
+      <c r="B33" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C33" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E33">
+        <v>Vélez</v>
+      </c>
+      <c r="E33" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F33" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <f>+'Reporte a FCCF'!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="H33">
+        <v>11</v>
+      </c>
+      <c r="H33" t="str">
         <f>+'Reporte a FCCF'!$C$16</f>
-        <v>0</v>
+        <v>LUCILA GRANATELLI</v>
       </c>
       <c r="I33">
         <f>+'Reporte a FCCF'!T16</f>
@@ -4980,37 +5188,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" spans="1:16">
+      <c r="A34" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B34">
+        <v>Primera A</v>
+      </c>
+      <c r="B34" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C34" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E34">
+        <v>Vélez</v>
+      </c>
+      <c r="E34" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F34" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <f>+'Reporte a FCCF'!$B$17</f>
-        <v>0</v>
-      </c>
-      <c r="H34">
+        <v>12</v>
+      </c>
+      <c r="H34" t="str">
         <f>+'Reporte a FCCF'!$C$17</f>
-        <v>0</v>
+        <v>MARIA PAZ GOMEZ</v>
       </c>
       <c r="I34">
         <f>+'Reporte a FCCF'!T17</f>
@@ -5045,37 +5253,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="35" spans="1:16">
+      <c r="A35" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B35">
+        <v>Primera A</v>
+      </c>
+      <c r="B35" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C35" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E35">
+        <v>Vélez</v>
+      </c>
+      <c r="E35" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F35" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <f>+'Reporte a FCCF'!$B$18</f>
-        <v>0</v>
-      </c>
-      <c r="H35">
+        <v>14</v>
+      </c>
+      <c r="H35" t="str">
         <f>+'Reporte a FCCF'!$C$18</f>
-        <v>0</v>
+        <v>LUCIANA BRINGAS</v>
       </c>
       <c r="I35">
         <f>+'Reporte a FCCF'!T18</f>
@@ -5110,37 +5318,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="36" spans="1:16">
+      <c r="A36" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B36">
+        <v>Primera A</v>
+      </c>
+      <c r="B36" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C36" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E36">
+        <v>Vélez</v>
+      </c>
+      <c r="E36" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F36" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <f>+'Reporte a FCCF'!$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="H36">
+        <v>15</v>
+      </c>
+      <c r="H36" t="str">
         <f>+'Reporte a FCCF'!$C$19</f>
-        <v>0</v>
+        <v>CANDELA THIM</v>
       </c>
       <c r="I36">
         <f>+'Reporte a FCCF'!T19</f>
@@ -5175,29 +5383,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="37" spans="1:16">
+      <c r="A37" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B37">
+        <v>Primera A</v>
+      </c>
+      <c r="B37" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C37" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E37">
+        <v>Vélez</v>
+      </c>
+      <c r="E37" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F37" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G37">
         <f>+'Reporte a FCCF'!$B$20</f>
@@ -5240,37 +5448,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="38" spans="1:16">
+      <c r="A38" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B38">
+        <v>Primera A</v>
+      </c>
+      <c r="B38" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C38" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E38">
+        <v>Vélez</v>
+      </c>
+      <c r="E38" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <f>+'Reporte a FCCF'!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="H38" t="str">
         <f>+'Reporte a FCCF'!$C$9</f>
-        <v>0</v>
+        <v>LUCIA COSTA</v>
       </c>
       <c r="I38">
         <f>+'Reporte a FCCF'!AB9</f>
@@ -5305,37 +5513,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39">
+    <row r="39" spans="1:16">
+      <c r="A39" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B39">
+        <v>Primera A</v>
+      </c>
+      <c r="B39" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C39" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E39">
+        <v>Vélez</v>
+      </c>
+      <c r="E39" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G39">
         <f>+'Reporte a FCCF'!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H39">
+        <v>5</v>
+      </c>
+      <c r="H39" t="str">
         <f>+'Reporte a FCCF'!$C$10</f>
-        <v>0</v>
+        <v>MARIELA ELIAS</v>
       </c>
       <c r="I39">
         <f>+'Reporte a FCCF'!AB10</f>
@@ -5370,37 +5578,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40">
+    <row r="40" spans="1:16">
+      <c r="A40" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B40">
+        <v>Primera A</v>
+      </c>
+      <c r="B40" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C40" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E40">
+        <v>Vélez</v>
+      </c>
+      <c r="E40" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F40" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <f>+'Reporte a FCCF'!$B$11</f>
-        <v>0</v>
-      </c>
-      <c r="H40">
+        <v>6</v>
+      </c>
+      <c r="H40" t="str">
         <f>+'Reporte a FCCF'!$C$11</f>
-        <v>0</v>
+        <v>MALENA ZUCCARINO</v>
       </c>
       <c r="I40">
         <f>+'Reporte a FCCF'!AB11</f>
@@ -5435,37 +5643,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41">
+    <row r="41" spans="1:16">
+      <c r="A41" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B41">
+        <v>Primera A</v>
+      </c>
+      <c r="B41" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C41" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E41">
+        <v>Vélez</v>
+      </c>
+      <c r="E41" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F41" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <f>+'Reporte a FCCF'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
+        <v>7</v>
+      </c>
+      <c r="H41" t="str">
         <f>+'Reporte a FCCF'!$C$12</f>
-        <v>0</v>
+        <v>JIMENA GARCIA</v>
       </c>
       <c r="I41">
         <f>+'Reporte a FCCF'!AB12</f>
@@ -5500,37 +5708,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42">
+    <row r="42" spans="1:16">
+      <c r="A42" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B42">
+        <v>Primera A</v>
+      </c>
+      <c r="B42" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C42" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C42" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E42">
+        <v>Vélez</v>
+      </c>
+      <c r="E42" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G42">
         <f>+'Reporte a FCCF'!$B$13</f>
-        <v>0</v>
-      </c>
-      <c r="H42">
+        <v>8</v>
+      </c>
+      <c r="H42" t="str">
         <f>+'Reporte a FCCF'!$C$13</f>
-        <v>0</v>
+        <v>SOFIA NAÓN</v>
       </c>
       <c r="I42">
         <f>+'Reporte a FCCF'!AB13</f>
@@ -5565,37 +5773,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43">
+    <row r="43" spans="1:16">
+      <c r="A43" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B43">
+        <v>Primera A</v>
+      </c>
+      <c r="B43" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C43" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C43" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E43">
+        <v>Vélez</v>
+      </c>
+      <c r="E43" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F43" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G43">
         <f>+'Reporte a FCCF'!$B$14</f>
-        <v>0</v>
-      </c>
-      <c r="H43">
+        <v>9</v>
+      </c>
+      <c r="H43" t="str">
         <f>+'Reporte a FCCF'!$C$14</f>
-        <v>0</v>
+        <v>VICTORIA FONTAN</v>
       </c>
       <c r="I43">
         <f>+'Reporte a FCCF'!AB14</f>
@@ -5630,37 +5838,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44">
+    <row r="44" spans="1:16">
+      <c r="A44" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B44">
+        <v>Primera A</v>
+      </c>
+      <c r="B44" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C44" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C44" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E44">
+        <v>Vélez</v>
+      </c>
+      <c r="E44" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G44">
         <f>+'Reporte a FCCF'!$B$15</f>
-        <v>0</v>
-      </c>
-      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="H44" t="str">
         <f>+'Reporte a FCCF'!$C$15</f>
-        <v>0</v>
+        <v>ZAHIRA HERRERA</v>
       </c>
       <c r="I44">
         <f>+'Reporte a FCCF'!AB15</f>
@@ -5695,37 +5903,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45">
+    <row r="45" spans="1:16">
+      <c r="A45" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B45">
+        <v>Primera A</v>
+      </c>
+      <c r="B45" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C45" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C45" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E45">
+        <v>Vélez</v>
+      </c>
+      <c r="E45" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G45">
         <f>+'Reporte a FCCF'!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="H45">
+        <v>11</v>
+      </c>
+      <c r="H45" t="str">
         <f>+'Reporte a FCCF'!$C$16</f>
-        <v>0</v>
+        <v>LUCILA GRANATELLI</v>
       </c>
       <c r="I45">
         <f>+'Reporte a FCCF'!AB16</f>
@@ -5760,37 +5968,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46">
+    <row r="46" spans="1:16">
+      <c r="A46" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B46">
+        <v>Primera A</v>
+      </c>
+      <c r="B46" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C46" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D46">
+      <c r="D46" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E46">
+        <v>Vélez</v>
+      </c>
+      <c r="E46" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F46" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G46">
         <f>+'Reporte a FCCF'!$B$17</f>
-        <v>0</v>
-      </c>
-      <c r="H46">
+        <v>12</v>
+      </c>
+      <c r="H46" t="str">
         <f>+'Reporte a FCCF'!$C$17</f>
-        <v>0</v>
+        <v>MARIA PAZ GOMEZ</v>
       </c>
       <c r="I46">
         <f>+'Reporte a FCCF'!AB17</f>
@@ -5825,37 +6033,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47">
+    <row r="47" spans="1:16">
+      <c r="A47" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B47">
+        <v>Primera A</v>
+      </c>
+      <c r="B47" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C47" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D47">
+      <c r="D47" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E47">
+        <v>Vélez</v>
+      </c>
+      <c r="E47" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G47">
         <f>+'Reporte a FCCF'!$B$18</f>
-        <v>0</v>
-      </c>
-      <c r="H47">
+        <v>14</v>
+      </c>
+      <c r="H47" t="str">
         <f>+'Reporte a FCCF'!$C$18</f>
-        <v>0</v>
+        <v>LUCIANA BRINGAS</v>
       </c>
       <c r="I47">
         <f>+'Reporte a FCCF'!AB18</f>
@@ -5890,37 +6098,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48">
+    <row r="48" spans="1:16">
+      <c r="A48" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B48">
+        <v>Primera A</v>
+      </c>
+      <c r="B48" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C48" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C48" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E48">
+        <v>Vélez</v>
+      </c>
+      <c r="E48" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G48">
         <f>+'Reporte a FCCF'!$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="H48">
+        <v>15</v>
+      </c>
+      <c r="H48" t="str">
         <f>+'Reporte a FCCF'!$C$19</f>
-        <v>0</v>
+        <v>CANDELA THIM</v>
       </c>
       <c r="I48">
         <f>+'Reporte a FCCF'!AB19</f>
@@ -5955,29 +6163,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49">
+    <row r="49" spans="1:16">
+      <c r="A49" t="str">
         <f>+'Reporte a FCCF'!$I$4</f>
-        <v>0</v>
-      </c>
-      <c r="B49">
+        <v>Primera A</v>
+      </c>
+      <c r="B49" t="str">
         <f>+'Reporte a FCCF'!$I$2</f>
-        <v>0</v>
-      </c>
-      <c r="C49" s="41">
+        <v>Apertura 2026</v>
+      </c>
+      <c r="C49" s="12">
         <f>+'Reporte a FCCF'!$Q$2</f>
         <v>0</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="str">
         <f>+'Reporte a FCCF'!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="E49">
+        <v>Vélez</v>
+      </c>
+      <c r="E49" t="str">
         <f>+'Reporte a FCCF'!$C$4</f>
-        <v>0</v>
+        <v>Avellaneda</v>
       </c>
       <c r="F49" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G49">
         <f>+'Reporte a FCCF'!$B$20</f>
@@ -6023,130 +6231,2722 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="tA17w0k+YvHyPXxLWzy6qRRDMCRhcPh9uJX6/XEnMFeIf9y3+atTF2v5moNRluH/IC2h94Za69xDtyttC2RUig==" saltValue="utg5HepvII5pUAKZkoYI+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;7&amp;K000000 ***Este documento está clasificado como USO INTERNO por MOVISTAR. ***This document is classified as INTERNAL USE by MOVISTAR.</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8F239-A587-4BE7-8D61-A7A5DF69584A}">
+  <dimension ref="B2:AQ24"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="35" width="6.7109375" customWidth="1"/>
+    <col min="36" max="43" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:43">
+      <c r="B2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="72" t="str">
+        <f>+'Reporte a FCCF'!C2</f>
+        <v>Vélez</v>
+      </c>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="72" t="str">
+        <f>+'Reporte a FCCF'!I2</f>
+        <v>Apertura 2026</v>
+      </c>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="74">
+        <f>+'Reporte a FCCF'!Q2</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="74"/>
+      <c r="S2" s="75"/>
+    </row>
+    <row r="3" spans="2:43" ht="7.5" customHeight="1"/>
+    <row r="4" spans="2:43">
+      <c r="B4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="72" t="str">
+        <f>+'Reporte a FCCF'!C4</f>
+        <v>Avellaneda</v>
+      </c>
+      <c r="D4" s="72"/>
+      <c r="E4" s="73"/>
+      <c r="G4" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="46"/>
+      <c r="I4" s="72" t="str">
+        <f>+'Reporte a FCCF'!I4</f>
+        <v>Primera A</v>
+      </c>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="73"/>
+    </row>
+    <row r="5" spans="2:43" ht="15" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:43" ht="15" thickBot="1">
+      <c r="D6" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="57"/>
+      <c r="AJ6" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="60"/>
+    </row>
+    <row r="7" spans="2:43" ht="15" customHeight="1">
+      <c r="B7" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="67"/>
+      <c r="I7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="S7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="U7" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC7" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF7" s="53"/>
+      <c r="AG7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH7" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ7" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL7" s="65"/>
+      <c r="AM7" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN7" s="65"/>
+      <c r="AO7" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP7" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ7" s="54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:43">
+      <c r="B8" s="69"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="52"/>
+      <c r="AC8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE8" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF8" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="63"/>
+      <c r="AJ8" s="64"/>
+      <c r="AK8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM8" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="AN8" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO8" s="61"/>
+      <c r="AP8" s="61"/>
+      <c r="AQ8" s="54"/>
+    </row>
+    <row r="9" spans="2:43" ht="30" customHeight="1">
+      <c r="B9" s="28">
+        <f>+'Reporte a FCCF'!B9</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f>+'Reporte a FCCF'!C9</f>
+        <v>LUCIA COSTA</v>
+      </c>
+      <c r="D9" s="28">
+        <f>+'Reporte a FCCF'!D9</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="30">
+        <f>+'Reporte a FCCF'!E9</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="30">
+        <f>+'Reporte a FCCF'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="30">
+        <f>+'Reporte a FCCF'!G9</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="30">
+        <f>+'Reporte a FCCF'!H9</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="30">
+        <f>+'Reporte a FCCF'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="30">
+        <f>+'Reporte a FCCF'!J9</f>
+        <v>2</v>
+      </c>
+      <c r="K9" s="31">
+        <f>+'Reporte a FCCF'!K9</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="28">
+        <f>+'Reporte a FCCF'!L9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="30">
+        <f>+'Reporte a FCCF'!M9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="30">
+        <f>+'Reporte a FCCF'!N9</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="30">
+        <f>+'Reporte a FCCF'!O9</f>
+        <v>1</v>
+      </c>
+      <c r="P9" s="30">
+        <f>+'Reporte a FCCF'!P9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="30">
+        <f>+'Reporte a FCCF'!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="30">
+        <f>+'Reporte a FCCF'!R9</f>
+        <v>1</v>
+      </c>
+      <c r="S9" s="31">
+        <f>+'Reporte a FCCF'!S9</f>
+        <v>5</v>
+      </c>
+      <c r="T9" s="28">
+        <f>+'Reporte a FCCF'!T9</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="30">
+        <f>+'Reporte a FCCF'!U9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="30">
+        <f>+'Reporte a FCCF'!V9</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="30">
+        <f>+'Reporte a FCCF'!W9</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="30">
+        <f>+'Reporte a FCCF'!X9</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="30">
+        <f>+'Reporte a FCCF'!Y9</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="30">
+        <f>+'Reporte a FCCF'!Z9</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="31">
+        <f>+'Reporte a FCCF'!AA9</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="28">
+        <f>+'Reporte a FCCF'!AB9</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" s="30">
+        <f>+'Reporte a FCCF'!AC9</f>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="30">
+        <f>+'Reporte a FCCF'!AD9</f>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="30">
+        <f>+'Reporte a FCCF'!AE9</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="30">
+        <f>+'Reporte a FCCF'!AF9</f>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="30">
+        <f>+'Reporte a FCCF'!AG9</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="30">
+        <f>+'Reporte a FCCF'!AH9</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="31">
+        <f>+'Reporte a FCCF'!AI9</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="8">
+        <f t="shared" ref="AJ9:AQ20" si="0">+D9+L9+T9+AB9</f>
+        <v>4</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AN9" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:43" ht="30" customHeight="1">
+      <c r="B10" s="28">
+        <f>+'Reporte a FCCF'!B10</f>
+        <v>5</v>
+      </c>
+      <c r="C10" s="29" t="str">
+        <f>+'Reporte a FCCF'!C10</f>
+        <v>MARIELA ELIAS</v>
+      </c>
+      <c r="D10" s="28">
+        <f>+'Reporte a FCCF'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="30">
+        <f>+'Reporte a FCCF'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="30">
+        <f>+'Reporte a FCCF'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30">
+        <f>+'Reporte a FCCF'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="30">
+        <f>+'Reporte a FCCF'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="30">
+        <f>+'Reporte a FCCF'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="30">
+        <f>+'Reporte a FCCF'!J10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="31">
+        <f>+'Reporte a FCCF'!K10</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="28">
+        <f>+'Reporte a FCCF'!L10</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="30">
+        <f>+'Reporte a FCCF'!M10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="30">
+        <f>+'Reporte a FCCF'!N10</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="30">
+        <f>+'Reporte a FCCF'!O10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="30">
+        <f>+'Reporte a FCCF'!P10</f>
+        <v>3</v>
+      </c>
+      <c r="Q10" s="30">
+        <f>+'Reporte a FCCF'!Q10</f>
+        <v>2</v>
+      </c>
+      <c r="R10" s="30">
+        <f>+'Reporte a FCCF'!R10</f>
+        <v>4</v>
+      </c>
+      <c r="S10" s="31">
+        <f>+'Reporte a FCCF'!S10</f>
+        <v>5</v>
+      </c>
+      <c r="T10" s="28">
+        <f>+'Reporte a FCCF'!T10</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="30">
+        <f>+'Reporte a FCCF'!U10</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="30">
+        <f>+'Reporte a FCCF'!V10</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="30">
+        <f>+'Reporte a FCCF'!W10</f>
+        <v>0</v>
+      </c>
+      <c r="X10" s="30">
+        <f>+'Reporte a FCCF'!X10</f>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="30">
+        <f>+'Reporte a FCCF'!Y10</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="30">
+        <f>+'Reporte a FCCF'!Z10</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="31">
+        <f>+'Reporte a FCCF'!AA10</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="28">
+        <f>+'Reporte a FCCF'!AB10</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="30">
+        <f>+'Reporte a FCCF'!AC10</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="30">
+        <f>+'Reporte a FCCF'!AD10</f>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="30">
+        <f>+'Reporte a FCCF'!AE10</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="30">
+        <f>+'Reporte a FCCF'!AF10</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="30">
+        <f>+'Reporte a FCCF'!AG10</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="30">
+        <f>+'Reporte a FCCF'!AH10</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="31">
+        <f>+'Reporte a FCCF'!AI10</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AO10" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AP10" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:43" ht="30" customHeight="1">
+      <c r="B11" s="28">
+        <f>+'Reporte a FCCF'!B11</f>
+        <v>6</v>
+      </c>
+      <c r="C11" s="29" t="str">
+        <f>+'Reporte a FCCF'!C11</f>
+        <v>MALENA ZUCCARINO</v>
+      </c>
+      <c r="D11" s="28">
+        <f>+'Reporte a FCCF'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="30">
+        <f>+'Reporte a FCCF'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <f>+'Reporte a FCCF'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <f>+'Reporte a FCCF'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="30">
+        <f>+'Reporte a FCCF'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="30">
+        <f>+'Reporte a FCCF'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="30">
+        <f>+'Reporte a FCCF'!J11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="31">
+        <f>+'Reporte a FCCF'!K11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="28">
+        <f>+'Reporte a FCCF'!L11</f>
+        <v>4</v>
+      </c>
+      <c r="M11" s="30">
+        <f>+'Reporte a FCCF'!M11</f>
+        <v>2</v>
+      </c>
+      <c r="N11" s="30">
+        <f>+'Reporte a FCCF'!N11</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="30">
+        <f>+'Reporte a FCCF'!O11</f>
+        <v>2</v>
+      </c>
+      <c r="P11" s="30">
+        <f>+'Reporte a FCCF'!P11</f>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="30">
+        <f>+'Reporte a FCCF'!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="30">
+        <f>+'Reporte a FCCF'!R11</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="31">
+        <f>+'Reporte a FCCF'!S11</f>
+        <v>3</v>
+      </c>
+      <c r="T11" s="28">
+        <f>+'Reporte a FCCF'!T11</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="30">
+        <f>+'Reporte a FCCF'!U11</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="30">
+        <f>+'Reporte a FCCF'!V11</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="30">
+        <f>+'Reporte a FCCF'!W11</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="30">
+        <f>+'Reporte a FCCF'!X11</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="30">
+        <f>+'Reporte a FCCF'!Y11</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="30">
+        <f>+'Reporte a FCCF'!Z11</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="31">
+        <f>+'Reporte a FCCF'!AA11</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="28">
+        <f>+'Reporte a FCCF'!AB11</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="30">
+        <f>+'Reporte a FCCF'!AC11</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="30">
+        <f>+'Reporte a FCCF'!AD11</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="30">
+        <f>+'Reporte a FCCF'!AE11</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="30">
+        <f>+'Reporte a FCCF'!AF11</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="30">
+        <f>+'Reporte a FCCF'!AG11</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="30">
+        <f>+'Reporte a FCCF'!AH11</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="31">
+        <f>+'Reporte a FCCF'!AI11</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK11" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AL11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AN11" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:43" ht="30" customHeight="1">
+      <c r="B12" s="28">
+        <f>+'Reporte a FCCF'!B12</f>
+        <v>7</v>
+      </c>
+      <c r="C12" s="29" t="str">
+        <f>+'Reporte a FCCF'!C12</f>
+        <v>JIMENA GARCIA</v>
+      </c>
+      <c r="D12" s="28">
+        <f>+'Reporte a FCCF'!D12</f>
+        <v>11</v>
+      </c>
+      <c r="E12" s="30">
+        <f>+'Reporte a FCCF'!E12</f>
+        <v>5</v>
+      </c>
+      <c r="F12" s="30">
+        <f>+'Reporte a FCCF'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="30">
+        <f>+'Reporte a FCCF'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="30">
+        <f>+'Reporte a FCCF'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="30">
+        <f>+'Reporte a FCCF'!I12</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="30">
+        <f>+'Reporte a FCCF'!J12</f>
+        <v>2</v>
+      </c>
+      <c r="K12" s="31">
+        <f>+'Reporte a FCCF'!K12</f>
+        <v>2</v>
+      </c>
+      <c r="L12" s="28">
+        <f>+'Reporte a FCCF'!L12</f>
+        <v>9</v>
+      </c>
+      <c r="M12" s="30">
+        <f>+'Reporte a FCCF'!M12</f>
+        <v>4</v>
+      </c>
+      <c r="N12" s="30">
+        <f>+'Reporte a FCCF'!N12</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="30">
+        <f>+'Reporte a FCCF'!O12</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="30">
+        <f>+'Reporte a FCCF'!P12</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="30">
+        <f>+'Reporte a FCCF'!Q12</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="30">
+        <f>+'Reporte a FCCF'!R12</f>
+        <v>1</v>
+      </c>
+      <c r="S12" s="31">
+        <f>+'Reporte a FCCF'!S12</f>
+        <v>1</v>
+      </c>
+      <c r="T12" s="28">
+        <f>+'Reporte a FCCF'!T12</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="30">
+        <f>+'Reporte a FCCF'!U12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="30">
+        <f>+'Reporte a FCCF'!V12</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="30">
+        <f>+'Reporte a FCCF'!W12</f>
+        <v>0</v>
+      </c>
+      <c r="X12" s="30">
+        <f>+'Reporte a FCCF'!X12</f>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="30">
+        <f>+'Reporte a FCCF'!Y12</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="30">
+        <f>+'Reporte a FCCF'!Z12</f>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="31">
+        <f>+'Reporte a FCCF'!AA12</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="28">
+        <f>+'Reporte a FCCF'!AB12</f>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="30">
+        <f>+'Reporte a FCCF'!AC12</f>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="30">
+        <f>+'Reporte a FCCF'!AD12</f>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="30">
+        <f>+'Reporte a FCCF'!AE12</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="30">
+        <f>+'Reporte a FCCF'!AF12</f>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="30">
+        <f>+'Reporte a FCCF'!AG12</f>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="30">
+        <f>+'Reporte a FCCF'!AH12</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="31">
+        <f>+'Reporte a FCCF'!AI12</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="AK12" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AL12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP12" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:43" ht="30" customHeight="1">
+      <c r="B13" s="28">
+        <f>+'Reporte a FCCF'!B13</f>
+        <v>8</v>
+      </c>
+      <c r="C13" s="29" t="str">
+        <f>+'Reporte a FCCF'!C13</f>
+        <v>SOFIA NAÓN</v>
+      </c>
+      <c r="D13" s="28">
+        <f>+'Reporte a FCCF'!D13</f>
+        <v>6</v>
+      </c>
+      <c r="E13" s="30">
+        <f>+'Reporte a FCCF'!E13</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="30">
+        <f>+'Reporte a FCCF'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <f>+'Reporte a FCCF'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="30">
+        <f>+'Reporte a FCCF'!H13</f>
+        <v>3</v>
+      </c>
+      <c r="I13" s="30">
+        <f>+'Reporte a FCCF'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="30">
+        <f>+'Reporte a FCCF'!J13</f>
+        <v>3</v>
+      </c>
+      <c r="K13" s="31">
+        <f>+'Reporte a FCCF'!K13</f>
+        <v>2</v>
+      </c>
+      <c r="L13" s="28">
+        <f>+'Reporte a FCCF'!L13</f>
+        <v>8</v>
+      </c>
+      <c r="M13" s="30">
+        <f>+'Reporte a FCCF'!M13</f>
+        <v>5</v>
+      </c>
+      <c r="N13" s="30">
+        <f>+'Reporte a FCCF'!N13</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="30">
+        <f>+'Reporte a FCCF'!O13</f>
+        <v>2</v>
+      </c>
+      <c r="P13" s="30">
+        <f>+'Reporte a FCCF'!P13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="30">
+        <f>+'Reporte a FCCF'!Q13</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="30">
+        <f>+'Reporte a FCCF'!R13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="31">
+        <f>+'Reporte a FCCF'!S13</f>
+        <v>3</v>
+      </c>
+      <c r="T13" s="28">
+        <f>+'Reporte a FCCF'!T13</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="30">
+        <f>+'Reporte a FCCF'!U13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="30">
+        <f>+'Reporte a FCCF'!V13</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="30">
+        <f>+'Reporte a FCCF'!W13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="30">
+        <f>+'Reporte a FCCF'!X13</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="30">
+        <f>+'Reporte a FCCF'!Y13</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="30">
+        <f>+'Reporte a FCCF'!Z13</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="31">
+        <f>+'Reporte a FCCF'!AA13</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="28">
+        <f>+'Reporte a FCCF'!AB13</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="30">
+        <f>+'Reporte a FCCF'!AC13</f>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="30">
+        <f>+'Reporte a FCCF'!AD13</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="30">
+        <f>+'Reporte a FCCF'!AE13</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="30">
+        <f>+'Reporte a FCCF'!AF13</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="30">
+        <f>+'Reporte a FCCF'!AG13</f>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="30">
+        <f>+'Reporte a FCCF'!AH13</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="31">
+        <f>+'Reporte a FCCF'!AI13</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="AK13" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="AL13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AN13" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AO13" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP13" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:43" ht="30" customHeight="1">
+      <c r="B14" s="28">
+        <f>+'Reporte a FCCF'!B14</f>
+        <v>9</v>
+      </c>
+      <c r="C14" s="29" t="str">
+        <f>+'Reporte a FCCF'!C14</f>
+        <v>VICTORIA FONTAN</v>
+      </c>
+      <c r="D14" s="28">
+        <f>+'Reporte a FCCF'!D14</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="30">
+        <f>+'Reporte a FCCF'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="30">
+        <f>+'Reporte a FCCF'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="30">
+        <f>+'Reporte a FCCF'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="30">
+        <f>+'Reporte a FCCF'!H14</f>
+        <v>7</v>
+      </c>
+      <c r="I14" s="30">
+        <f>+'Reporte a FCCF'!I14</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="30">
+        <f>+'Reporte a FCCF'!J14</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="31">
+        <f>+'Reporte a FCCF'!K14</f>
+        <v>3</v>
+      </c>
+      <c r="L14" s="28">
+        <f>+'Reporte a FCCF'!L14</f>
+        <v>4</v>
+      </c>
+      <c r="M14" s="30">
+        <f>+'Reporte a FCCF'!M14</f>
+        <v>2</v>
+      </c>
+      <c r="N14" s="30">
+        <f>+'Reporte a FCCF'!N14</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="30">
+        <f>+'Reporte a FCCF'!O14</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="30">
+        <f>+'Reporte a FCCF'!P14</f>
+        <v>10</v>
+      </c>
+      <c r="Q14" s="30">
+        <f>+'Reporte a FCCF'!Q14</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="30">
+        <f>+'Reporte a FCCF'!R14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="31">
+        <f>+'Reporte a FCCF'!S14</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="28">
+        <f>+'Reporte a FCCF'!T14</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="30">
+        <f>+'Reporte a FCCF'!U14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="30">
+        <f>+'Reporte a FCCF'!V14</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="30">
+        <f>+'Reporte a FCCF'!W14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="30">
+        <f>+'Reporte a FCCF'!X14</f>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="30">
+        <f>+'Reporte a FCCF'!Y14</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="30">
+        <f>+'Reporte a FCCF'!Z14</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="31">
+        <f>+'Reporte a FCCF'!AA14</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="28">
+        <f>+'Reporte a FCCF'!AB14</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="30">
+        <f>+'Reporte a FCCF'!AC14</f>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="30">
+        <f>+'Reporte a FCCF'!AD14</f>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="30">
+        <f>+'Reporte a FCCF'!AE14</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="30">
+        <f>+'Reporte a FCCF'!AF14</f>
+        <v>0</v>
+      </c>
+      <c r="AG14" s="30">
+        <f>+'Reporte a FCCF'!AG14</f>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="30">
+        <f>+'Reporte a FCCF'!AH14</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="31">
+        <f>+'Reporte a FCCF'!AI14</f>
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AK14" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AL14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AO14" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AP14" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:43" ht="30" customHeight="1">
+      <c r="B15" s="28">
+        <f>+'Reporte a FCCF'!B15</f>
+        <v>10</v>
+      </c>
+      <c r="C15" s="29" t="str">
+        <f>+'Reporte a FCCF'!C15</f>
+        <v>ZAHIRA HERRERA</v>
+      </c>
+      <c r="D15" s="28">
+        <f>+'Reporte a FCCF'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="30">
+        <f>+'Reporte a FCCF'!E15</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <f>+'Reporte a FCCF'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="30">
+        <f>+'Reporte a FCCF'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="30">
+        <f>+'Reporte a FCCF'!H15</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="30">
+        <f>+'Reporte a FCCF'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="30">
+        <f>+'Reporte a FCCF'!J15</f>
+        <v>1</v>
+      </c>
+      <c r="K15" s="31">
+        <f>+'Reporte a FCCF'!K15</f>
+        <v>3</v>
+      </c>
+      <c r="L15" s="28">
+        <f>+'Reporte a FCCF'!L15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="30">
+        <f>+'Reporte a FCCF'!M15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="30">
+        <f>+'Reporte a FCCF'!N15</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="30">
+        <f>+'Reporte a FCCF'!O15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="30">
+        <f>+'Reporte a FCCF'!P15</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="30">
+        <f>+'Reporte a FCCF'!Q15</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="30">
+        <f>+'Reporte a FCCF'!R15</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="31">
+        <f>+'Reporte a FCCF'!S15</f>
+        <v>3</v>
+      </c>
+      <c r="T15" s="28">
+        <f>+'Reporte a FCCF'!T15</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="30">
+        <f>+'Reporte a FCCF'!U15</f>
+        <v>0</v>
+      </c>
+      <c r="V15" s="30">
+        <f>+'Reporte a FCCF'!V15</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="30">
+        <f>+'Reporte a FCCF'!W15</f>
+        <v>0</v>
+      </c>
+      <c r="X15" s="30">
+        <f>+'Reporte a FCCF'!X15</f>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="30">
+        <f>+'Reporte a FCCF'!Y15</f>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="30">
+        <f>+'Reporte a FCCF'!Z15</f>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="31">
+        <f>+'Reporte a FCCF'!AA15</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="28">
+        <f>+'Reporte a FCCF'!AB15</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="30">
+        <f>+'Reporte a FCCF'!AC15</f>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="30">
+        <f>+'Reporte a FCCF'!AD15</f>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="30">
+        <f>+'Reporte a FCCF'!AE15</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="30">
+        <f>+'Reporte a FCCF'!AF15</f>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="30">
+        <f>+'Reporte a FCCF'!AG15</f>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="30">
+        <f>+'Reporte a FCCF'!AH15</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="31">
+        <f>+'Reporte a FCCF'!AI15</f>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO15" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP15" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:43" ht="30" customHeight="1">
+      <c r="B16" s="28">
+        <f>+'Reporte a FCCF'!B16</f>
+        <v>11</v>
+      </c>
+      <c r="C16" s="29" t="str">
+        <f>+'Reporte a FCCF'!C16</f>
+        <v>LUCILA GRANATELLI</v>
+      </c>
+      <c r="D16" s="28">
+        <f>+'Reporte a FCCF'!D16</f>
+        <v>9</v>
+      </c>
+      <c r="E16" s="30">
+        <f>+'Reporte a FCCF'!E16</f>
+        <v>6</v>
+      </c>
+      <c r="F16" s="30">
+        <f>+'Reporte a FCCF'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30">
+        <f>+'Reporte a FCCF'!G16</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="30">
+        <f>+'Reporte a FCCF'!H16</f>
+        <v>1</v>
+      </c>
+      <c r="I16" s="30">
+        <f>+'Reporte a FCCF'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="30">
+        <f>+'Reporte a FCCF'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="31">
+        <f>+'Reporte a FCCF'!K16</f>
+        <v>4</v>
+      </c>
+      <c r="L16" s="28">
+        <f>+'Reporte a FCCF'!L16</f>
+        <v>7</v>
+      </c>
+      <c r="M16" s="30">
+        <f>+'Reporte a FCCF'!M16</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="30">
+        <f>+'Reporte a FCCF'!N16</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="30">
+        <f>+'Reporte a FCCF'!O16</f>
+        <v>2</v>
+      </c>
+      <c r="P16" s="30">
+        <f>+'Reporte a FCCF'!P16</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="30">
+        <f>+'Reporte a FCCF'!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="30">
+        <f>+'Reporte a FCCF'!R16</f>
+        <v>1</v>
+      </c>
+      <c r="S16" s="31">
+        <f>+'Reporte a FCCF'!S16</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="28">
+        <f>+'Reporte a FCCF'!T16</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="30">
+        <f>+'Reporte a FCCF'!U16</f>
+        <v>0</v>
+      </c>
+      <c r="V16" s="30">
+        <f>+'Reporte a FCCF'!V16</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="30">
+        <f>+'Reporte a FCCF'!W16</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="30">
+        <f>+'Reporte a FCCF'!X16</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="30">
+        <f>+'Reporte a FCCF'!Y16</f>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="30">
+        <f>+'Reporte a FCCF'!Z16</f>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="31">
+        <f>+'Reporte a FCCF'!AA16</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="28">
+        <f>+'Reporte a FCCF'!AB16</f>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="30">
+        <f>+'Reporte a FCCF'!AC16</f>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="30">
+        <f>+'Reporte a FCCF'!AD16</f>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="30">
+        <f>+'Reporte a FCCF'!AE16</f>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="30">
+        <f>+'Reporte a FCCF'!AF16</f>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="30">
+        <f>+'Reporte a FCCF'!AG16</f>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="30">
+        <f>+'Reporte a FCCF'!AH16</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="31">
+        <f>+'Reporte a FCCF'!AI16</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="AK16" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AL16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="AN16" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP16" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:43" ht="30" customHeight="1">
+      <c r="B17" s="28">
+        <f>+'Reporte a FCCF'!B17</f>
+        <v>12</v>
+      </c>
+      <c r="C17" s="29" t="str">
+        <f>+'Reporte a FCCF'!C17</f>
+        <v>MARIA PAZ GOMEZ</v>
+      </c>
+      <c r="D17" s="28">
+        <f>+'Reporte a FCCF'!D17</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="30">
+        <f>+'Reporte a FCCF'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
+        <f>+'Reporte a FCCF'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="30">
+        <f>+'Reporte a FCCF'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="30">
+        <f>+'Reporte a FCCF'!H17</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="30">
+        <f>+'Reporte a FCCF'!I17</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="30">
+        <f>+'Reporte a FCCF'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="31">
+        <f>+'Reporte a FCCF'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="28">
+        <f>+'Reporte a FCCF'!L17</f>
+        <v>10</v>
+      </c>
+      <c r="M17" s="30">
+        <f>+'Reporte a FCCF'!M17</f>
+        <v>5</v>
+      </c>
+      <c r="N17" s="30">
+        <f>+'Reporte a FCCF'!N17</f>
+        <v>2</v>
+      </c>
+      <c r="O17" s="30">
+        <f>+'Reporte a FCCF'!O17</f>
+        <v>1</v>
+      </c>
+      <c r="P17" s="30">
+        <f>+'Reporte a FCCF'!P17</f>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="30">
+        <f>+'Reporte a FCCF'!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="30">
+        <f>+'Reporte a FCCF'!R17</f>
+        <v>1</v>
+      </c>
+      <c r="S17" s="31">
+        <f>+'Reporte a FCCF'!S17</f>
+        <v>1</v>
+      </c>
+      <c r="T17" s="28">
+        <f>+'Reporte a FCCF'!T17</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="30">
+        <f>+'Reporte a FCCF'!U17</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="30">
+        <f>+'Reporte a FCCF'!V17</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="30">
+        <f>+'Reporte a FCCF'!W17</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="30">
+        <f>+'Reporte a FCCF'!X17</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="30">
+        <f>+'Reporte a FCCF'!Y17</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="30">
+        <f>+'Reporte a FCCF'!Z17</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="31">
+        <f>+'Reporte a FCCF'!AA17</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="28">
+        <f>+'Reporte a FCCF'!AB17</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="30">
+        <f>+'Reporte a FCCF'!AC17</f>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="30">
+        <f>+'Reporte a FCCF'!AD17</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="30">
+        <f>+'Reporte a FCCF'!AE17</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="30">
+        <f>+'Reporte a FCCF'!AF17</f>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="30">
+        <f>+'Reporte a FCCF'!AG17</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="30">
+        <f>+'Reporte a FCCF'!AH17</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="31">
+        <f>+'Reporte a FCCF'!AI17</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="AK17" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AL17" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AM17" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN17" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO17" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP17" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:43" ht="30" customHeight="1">
+      <c r="B18" s="28">
+        <f>+'Reporte a FCCF'!B18</f>
+        <v>14</v>
+      </c>
+      <c r="C18" s="29" t="str">
+        <f>+'Reporte a FCCF'!C18</f>
+        <v>LUCIANA BRINGAS</v>
+      </c>
+      <c r="D18" s="28">
+        <f>+'Reporte a FCCF'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="30">
+        <f>+'Reporte a FCCF'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="30">
+        <f>+'Reporte a FCCF'!F18</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="30">
+        <f>+'Reporte a FCCF'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="30">
+        <f>+'Reporte a FCCF'!H18</f>
+        <v>1</v>
+      </c>
+      <c r="I18" s="30">
+        <f>+'Reporte a FCCF'!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="30">
+        <f>+'Reporte a FCCF'!J18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="31">
+        <f>+'Reporte a FCCF'!K18</f>
+        <v>1</v>
+      </c>
+      <c r="L18" s="28">
+        <f>+'Reporte a FCCF'!L18</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="30">
+        <f>+'Reporte a FCCF'!M18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="30">
+        <f>+'Reporte a FCCF'!N18</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="30">
+        <f>+'Reporte a FCCF'!O18</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="30">
+        <f>+'Reporte a FCCF'!P18</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="30">
+        <f>+'Reporte a FCCF'!Q18</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="30">
+        <f>+'Reporte a FCCF'!R18</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="31">
+        <f>+'Reporte a FCCF'!S18</f>
+        <v>4</v>
+      </c>
+      <c r="T18" s="28">
+        <f>+'Reporte a FCCF'!T18</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="30">
+        <f>+'Reporte a FCCF'!U18</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="30">
+        <f>+'Reporte a FCCF'!V18</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="30">
+        <f>+'Reporte a FCCF'!W18</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="30">
+        <f>+'Reporte a FCCF'!X18</f>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="30">
+        <f>+'Reporte a FCCF'!Y18</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="30">
+        <f>+'Reporte a FCCF'!Z18</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="31">
+        <f>+'Reporte a FCCF'!AA18</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="28">
+        <f>+'Reporte a FCCF'!AB18</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="30">
+        <f>+'Reporte a FCCF'!AC18</f>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="30">
+        <f>+'Reporte a FCCF'!AD18</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="30">
+        <f>+'Reporte a FCCF'!AE18</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="30">
+        <f>+'Reporte a FCCF'!AF18</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="30">
+        <f>+'Reporte a FCCF'!AG18</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="30">
+        <f>+'Reporte a FCCF'!AH18</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="31">
+        <f>+'Reporte a FCCF'!AI18</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AO18" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:43" ht="30" customHeight="1">
+      <c r="B19" s="28">
+        <f>+'Reporte a FCCF'!B19</f>
+        <v>15</v>
+      </c>
+      <c r="C19" s="29" t="str">
+        <f>+'Reporte a FCCF'!C19</f>
+        <v>CANDELA THIM</v>
+      </c>
+      <c r="D19" s="28">
+        <f>+'Reporte a FCCF'!D19</f>
+        <v>4</v>
+      </c>
+      <c r="E19" s="30">
+        <f>+'Reporte a FCCF'!E19</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="30">
+        <f>+'Reporte a FCCF'!F19</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="30">
+        <f>+'Reporte a FCCF'!G19</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="30">
+        <f>+'Reporte a FCCF'!H19</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="30">
+        <f>+'Reporte a FCCF'!I19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="30">
+        <f>+'Reporte a FCCF'!J19</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="31">
+        <f>+'Reporte a FCCF'!K19</f>
+        <v>2</v>
+      </c>
+      <c r="L19" s="28">
+        <f>+'Reporte a FCCF'!L19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="30">
+        <f>+'Reporte a FCCF'!M19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="30">
+        <f>+'Reporte a FCCF'!N19</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="30">
+        <f>+'Reporte a FCCF'!O19</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="30">
+        <f>+'Reporte a FCCF'!P19</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="30">
+        <f>+'Reporte a FCCF'!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="30">
+        <f>+'Reporte a FCCF'!R19</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="31">
+        <f>+'Reporte a FCCF'!S19</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="28">
+        <f>+'Reporte a FCCF'!T19</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="30">
+        <f>+'Reporte a FCCF'!U19</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="30">
+        <f>+'Reporte a FCCF'!V19</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="30">
+        <f>+'Reporte a FCCF'!W19</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="30">
+        <f>+'Reporte a FCCF'!X19</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="30">
+        <f>+'Reporte a FCCF'!Y19</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="30">
+        <f>+'Reporte a FCCF'!Z19</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="31">
+        <f>+'Reporte a FCCF'!AA19</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="28">
+        <f>+'Reporte a FCCF'!AB19</f>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="30">
+        <f>+'Reporte a FCCF'!AC19</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="30">
+        <f>+'Reporte a FCCF'!AD19</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="30">
+        <f>+'Reporte a FCCF'!AE19</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="30">
+        <f>+'Reporte a FCCF'!AF19</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="30">
+        <f>+'Reporte a FCCF'!AG19</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="30">
+        <f>+'Reporte a FCCF'!AH19</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="31">
+        <f>+'Reporte a FCCF'!AI19</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AK19" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL19" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN19" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:43" ht="30" customHeight="1" thickBot="1">
+      <c r="B20" s="32">
+        <f>+'Reporte a FCCF'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="33">
+        <f>+'Reporte a FCCF'!C20</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="32">
+        <f>+'Reporte a FCCF'!D20</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="34">
+        <f>+'Reporte a FCCF'!E20</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="34">
+        <f>+'Reporte a FCCF'!F20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="34">
+        <f>+'Reporte a FCCF'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="34">
+        <f>+'Reporte a FCCF'!H20</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="34">
+        <f>+'Reporte a FCCF'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="34">
+        <f>+'Reporte a FCCF'!J20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="35">
+        <f>+'Reporte a FCCF'!K20</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="32">
+        <f>+'Reporte a FCCF'!L20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="34">
+        <f>+'Reporte a FCCF'!M20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="34">
+        <f>+'Reporte a FCCF'!N20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="34">
+        <f>+'Reporte a FCCF'!O20</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="34">
+        <f>+'Reporte a FCCF'!P20</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="34">
+        <f>+'Reporte a FCCF'!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="34">
+        <f>+'Reporte a FCCF'!R20</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="35">
+        <f>+'Reporte a FCCF'!S20</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="32">
+        <f>+'Reporte a FCCF'!T20</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="34">
+        <f>+'Reporte a FCCF'!U20</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="34">
+        <f>+'Reporte a FCCF'!V20</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="34">
+        <f>+'Reporte a FCCF'!W20</f>
+        <v>0</v>
+      </c>
+      <c r="X20" s="34">
+        <f>+'Reporte a FCCF'!X20</f>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="34">
+        <f>+'Reporte a FCCF'!Y20</f>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="34">
+        <f>+'Reporte a FCCF'!Z20</f>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="35">
+        <f>+'Reporte a FCCF'!AA20</f>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="32">
+        <f>+'Reporte a FCCF'!AB20</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="34">
+        <f>+'Reporte a FCCF'!AC20</f>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="34">
+        <f>+'Reporte a FCCF'!AD20</f>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="34">
+        <f>+'Reporte a FCCF'!AE20</f>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="34">
+        <f>+'Reporte a FCCF'!AF20</f>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="34">
+        <f>+'Reporte a FCCF'!AG20</f>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="34">
+        <f>+'Reporte a FCCF'!AH20</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="35">
+        <f>+'Reporte a FCCF'!AI20</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:43" ht="7.5" customHeight="1" thickBot="1"/>
+    <row r="22" spans="2:43" ht="30" customHeight="1" thickBot="1">
+      <c r="B22" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="22">
+        <f>SUM(D9:D20)</f>
+        <v>36</v>
+      </c>
+      <c r="E22" s="23">
+        <f t="shared" ref="E22:AQ22" si="1">SUM(E9:E20)</f>
+        <v>16</v>
+      </c>
+      <c r="F22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H22" s="23">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J22" s="23">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K22" s="24">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L22" s="25">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="M22" s="26">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="N22" s="26">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O22" s="26">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="P22" s="26">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="Q22" s="26">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="R22" s="26">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="S22" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="T22" s="22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="22">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="AK22" s="23">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="AL22" s="23">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AM22" s="23">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="AN22" s="23">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AO22" s="23">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="AP22" s="23">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="AQ22" s="24">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:43" ht="7.5" customHeight="1"/>
+    <row r="24" spans="2:43">
+      <c r="B24" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="1kpptv5JGLbrjer90pDNWKHDrmkBTZWsDdKuDsPMozln2Qa6TQdKHHm5pkQ8LlNJHX8tj0rTHhzX6JQqU5BCIQ==" saltValue="ba+XjhXGlcxToBZ92nemaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="45">
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AM7:AN7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="T6:AA6"/>
+    <mergeCell ref="AB6:AI6"/>
+    <mergeCell ref="AJ6:AQ6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:N4"/>
+  </mergeCells>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:S2" xr:uid="{3E52C4E6-48C3-4D05-AD0B-8557B27D9354}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;7&amp;K000000 ***Este documento está clasificado como USO INTERNO por MOVISTAR. ***This document is classified as INTERNAL USE by MOVISTAR.</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF447CB7-1742-49BF-9A57-912D33ED9AC8}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="41">
+        <v>52</v>
+      </c>
+      <c r="G1" s="12">
         <v>45372</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="C3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="C4" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="C5" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="C6" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="C7" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="C8" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="C9" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="C10" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="C11" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="C12" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="C13" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="E14" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6156,5 +8956,14 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;7&amp;K000000 ***Este documento está clasificado como USO INTERNO por MOVISTAR. ***This document is classified as INTERNAL USE by MOVISTAR.</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ae67402c-8836-4bc5-8dc7-52e17881ec87}" enabled="1" method="Standard" siteId="{17d02e16-8b83-4168-ba0d-c61ac0d093a6}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>